--- a/research/traditional_assets/database/data/reunion/reunion_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/reunion/reunion_real_estate_general_diversified.xlsx
@@ -1197,7 +1197,7 @@
         <v>1.09922897355227</v>
       </c>
       <c r="Z2">
-        <v>0.81191131271358</v>
+        <v>0.811911312713581</v>
       </c>
       <c r="AA2">
         <v>191.4</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07622766467188903</v>
+        <v>0.07606806703257701</v>
       </c>
       <c r="C2">
-        <v>306.4413459743222</v>
+        <v>303.8275951951164</v>
       </c>
       <c r="D2">
-        <v>278.0413459743222</v>
+        <v>278.6575951951165</v>
       </c>
       <c r="E2">
-        <v>-191.4</v>
+        <v>-188.17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="G2">
         <v>28.4</v>
@@ -1451,28 +1451,28 @@
         <v>33.837</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.162469</v>
       </c>
       <c r="N2">
-        <v>33.837</v>
+        <v>33.674531</v>
       </c>
       <c r="O2">
-        <v>8.57570988772966</v>
+        <v>8.534533453360492</v>
       </c>
       <c r="P2">
-        <v>25.26129011227034</v>
+        <v>25.13999754663951</v>
       </c>
       <c r="Q2">
-        <v>26.04929011227035</v>
+        <v>25.92799754663951</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07622766467188903</v>
+        <v>0.07645711944801434</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5309801549172368</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.2674233238341</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07606806703257701</v>
+        <v>0.07590846939326501</v>
       </c>
       <c r="C3">
-        <v>303.8275951951164</v>
+        <v>301.2165821862607</v>
       </c>
       <c r="D3">
-        <v>278.6575951951165</v>
+        <v>279.2765821862607</v>
       </c>
       <c r="E3">
-        <v>-188.17</v>
+        <v>-184.94</v>
       </c>
       <c r="F3">
-        <v>3.23</v>
+        <v>6.46</v>
       </c>
       <c r="G3">
         <v>28.4</v>
@@ -1533,28 +1533,28 @@
         <v>33.837</v>
       </c>
       <c r="M3">
-        <v>0.162469</v>
+        <v>0.324938</v>
       </c>
       <c r="N3">
-        <v>33.674531</v>
+        <v>33.512062</v>
       </c>
       <c r="O3">
-        <v>8.534533453360492</v>
+        <v>8.493357018991322</v>
       </c>
       <c r="P3">
-        <v>25.13999754663951</v>
+        <v>25.01870498100868</v>
       </c>
       <c r="Q3">
-        <v>25.92799754663951</v>
+        <v>25.80670498100868</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07645711944801434</v>
+        <v>0.07669125697467283</v>
       </c>
       <c r="T3">
-        <v>0.5309801549172368</v>
+        <v>0.5350354080661139</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.2674233238341</v>
+        <v>104.133711661917</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07590846939326501</v>
+        <v>0.07574887175395301</v>
       </c>
       <c r="C4">
-        <v>301.2165821862607</v>
+        <v>298.6083252327434</v>
       </c>
       <c r="D4">
-        <v>279.2765821862607</v>
+        <v>279.8983252327434</v>
       </c>
       <c r="E4">
-        <v>-184.94</v>
+        <v>-181.71</v>
       </c>
       <c r="F4">
-        <v>6.46</v>
+        <v>9.69</v>
       </c>
       <c r="G4">
         <v>28.4</v>
@@ -1615,28 +1615,28 @@
         <v>33.837</v>
       </c>
       <c r="M4">
-        <v>0.324938</v>
+        <v>0.4874069999999999</v>
       </c>
       <c r="N4">
-        <v>33.512062</v>
+        <v>33.34959300000001</v>
       </c>
       <c r="O4">
-        <v>8.493357018991322</v>
+        <v>8.452180584622155</v>
       </c>
       <c r="P4">
-        <v>25.01870498100868</v>
+        <v>24.89741241537785</v>
       </c>
       <c r="Q4">
-        <v>25.80670498100868</v>
+        <v>25.68541241537785</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07669125697467283</v>
+        <v>0.07693022207920056</v>
       </c>
       <c r="T4">
-        <v>0.5350354080661139</v>
+        <v>0.5391742746819781</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.133711661917</v>
+        <v>69.42247444127806</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07574887175395301</v>
+        <v>0.075589274114641</v>
       </c>
       <c r="C5">
-        <v>298.6083252327434</v>
+        <v>296.0028427827447</v>
       </c>
       <c r="D5">
-        <v>279.8983252327434</v>
+        <v>280.5228427827448</v>
       </c>
       <c r="E5">
-        <v>-181.71</v>
+        <v>-178.48</v>
       </c>
       <c r="F5">
-        <v>9.69</v>
+        <v>12.92</v>
       </c>
       <c r="G5">
         <v>28.4</v>
@@ -1697,28 +1697,28 @@
         <v>33.837</v>
       </c>
       <c r="M5">
-        <v>0.4874069999999999</v>
+        <v>0.649876</v>
       </c>
       <c r="N5">
-        <v>33.34959300000001</v>
+        <v>33.187124</v>
       </c>
       <c r="O5">
-        <v>8.452180584622155</v>
+        <v>8.411004150252987</v>
       </c>
       <c r="P5">
-        <v>24.89741241537785</v>
+        <v>24.77611984974702</v>
       </c>
       <c r="Q5">
-        <v>25.68541241537785</v>
+        <v>25.56411984974702</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07693022207920056</v>
+        <v>0.07717416562340595</v>
       </c>
       <c r="T5">
-        <v>0.5391742746819781</v>
+        <v>0.5433993676856729</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.42247444127806</v>
+        <v>52.06685583095852</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.075589274114641</v>
+        <v>0.07542967647532897</v>
       </c>
       <c r="C6">
-        <v>296.0028427827447</v>
+        <v>293.400153449462</v>
       </c>
       <c r="D6">
-        <v>280.5228427827448</v>
+        <v>281.150153449462</v>
       </c>
       <c r="E6">
-        <v>-178.48</v>
+        <v>-175.25</v>
       </c>
       <c r="F6">
-        <v>12.92</v>
+        <v>16.15</v>
       </c>
       <c r="G6">
         <v>28.4</v>
@@ -1779,28 +1779,28 @@
         <v>33.837</v>
       </c>
       <c r="M6">
-        <v>0.649876</v>
+        <v>0.8123450000000001</v>
       </c>
       <c r="N6">
-        <v>33.187124</v>
+        <v>33.024655</v>
       </c>
       <c r="O6">
-        <v>8.411004150252987</v>
+        <v>8.369827715883819</v>
       </c>
       <c r="P6">
-        <v>24.77611984974702</v>
+        <v>24.65482728411618</v>
       </c>
       <c r="Q6">
-        <v>25.56411984974702</v>
+        <v>25.44282728411618</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07717416562340595</v>
+        <v>0.07742324482117355</v>
       </c>
       <c r="T6">
-        <v>0.5433993676856729</v>
+        <v>0.547713410015761</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.06685583095852</v>
+        <v>41.65348466476681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07542967647532897</v>
+        <v>0.07527007883601697</v>
       </c>
       <c r="C7">
-        <v>293.400153449462</v>
+        <v>290.8002760129579</v>
       </c>
       <c r="D7">
-        <v>281.150153449462</v>
+        <v>281.7802760129579</v>
       </c>
       <c r="E7">
-        <v>-175.25</v>
+        <v>-172.02</v>
       </c>
       <c r="F7">
-        <v>16.15</v>
+        <v>19.38</v>
       </c>
       <c r="G7">
         <v>28.4</v>
@@ -1861,28 +1861,28 @@
         <v>33.837</v>
       </c>
       <c r="M7">
-        <v>0.8123450000000001</v>
+        <v>0.9748140000000001</v>
       </c>
       <c r="N7">
-        <v>33.024655</v>
+        <v>32.862186</v>
       </c>
       <c r="O7">
-        <v>8.369827715883819</v>
+        <v>8.328651281514649</v>
       </c>
       <c r="P7">
-        <v>24.65482728411618</v>
+        <v>24.53353471848535</v>
       </c>
       <c r="Q7">
-        <v>25.44282728411618</v>
+        <v>25.32153471848535</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07742324482117355</v>
+        <v>0.07767762357634048</v>
       </c>
       <c r="T7">
-        <v>0.547713410015761</v>
+        <v>0.5521192404805321</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.65348466476681</v>
+        <v>34.71123722063901</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07527007883601697</v>
+        <v>0.07511048119670496</v>
       </c>
       <c r="C8">
-        <v>290.8002760129579</v>
+        <v>288.2032294220356</v>
       </c>
       <c r="D8">
-        <v>281.7802760129579</v>
+        <v>282.4132294220357</v>
       </c>
       <c r="E8">
-        <v>-172.02</v>
+        <v>-168.79</v>
       </c>
       <c r="F8">
-        <v>19.38</v>
+        <v>22.61</v>
       </c>
       <c r="G8">
         <v>28.4</v>
@@ -1943,28 +1943,28 @@
         <v>33.837</v>
       </c>
       <c r="M8">
-        <v>0.9748139999999998</v>
+        <v>1.137283</v>
       </c>
       <c r="N8">
-        <v>32.862186</v>
+        <v>32.69971700000001</v>
       </c>
       <c r="O8">
-        <v>8.328651281514649</v>
+        <v>8.287474847145482</v>
       </c>
       <c r="P8">
-        <v>24.53353471848535</v>
+        <v>24.41224215285452</v>
       </c>
       <c r="Q8">
-        <v>25.32153471848535</v>
+        <v>25.20024215285452</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07767762357634048</v>
+        <v>0.07793747284237119</v>
       </c>
       <c r="T8">
-        <v>0.5521192404805321</v>
+        <v>0.5566198199875562</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.71123722063902</v>
+        <v>29.75248904626202</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07511048119670495</v>
+        <v>0.07495088355739295</v>
       </c>
       <c r="C9">
-        <v>288.2032294220357</v>
+        <v>285.6090327961379</v>
       </c>
       <c r="D9">
-        <v>282.4132294220357</v>
+        <v>283.0490327961379</v>
       </c>
       <c r="E9">
-        <v>-168.79</v>
+        <v>-165.56</v>
       </c>
       <c r="F9">
-        <v>22.61</v>
+        <v>25.84</v>
       </c>
       <c r="G9">
         <v>28.4</v>
@@ -2025,28 +2025,28 @@
         <v>33.837</v>
       </c>
       <c r="M9">
-        <v>1.137283</v>
+        <v>1.299752</v>
       </c>
       <c r="N9">
-        <v>32.69971700000001</v>
+        <v>32.53724800000001</v>
       </c>
       <c r="O9">
-        <v>8.287474847145482</v>
+        <v>8.246298412776314</v>
       </c>
       <c r="P9">
-        <v>24.41224215285452</v>
+        <v>24.29094958722369</v>
       </c>
       <c r="Q9">
-        <v>25.20024215285452</v>
+        <v>25.07894958722369</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07793747284237119</v>
+        <v>0.07820297100548954</v>
       </c>
       <c r="T9">
-        <v>0.5566198199875562</v>
+        <v>0.5612182381795155</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.75248904626202</v>
+        <v>26.03342791547927</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07495088355739295</v>
+        <v>0.07479128591808096</v>
       </c>
       <c r="C10">
-        <v>285.6090327961379</v>
+        <v>283.0177054272716</v>
       </c>
       <c r="D10">
-        <v>283.0490327961379</v>
+        <v>283.6877054272716</v>
       </c>
       <c r="E10">
-        <v>-165.56</v>
+        <v>-162.33</v>
       </c>
       <c r="F10">
-        <v>25.84</v>
+        <v>29.07</v>
       </c>
       <c r="G10">
         <v>28.4</v>
@@ -2107,28 +2107,28 @@
         <v>33.837</v>
       </c>
       <c r="M10">
-        <v>1.299752</v>
+        <v>1.462221</v>
       </c>
       <c r="N10">
-        <v>32.53724800000001</v>
+        <v>32.374779</v>
       </c>
       <c r="O10">
-        <v>8.246298412776314</v>
+        <v>8.205121978407146</v>
       </c>
       <c r="P10">
-        <v>24.29094958722369</v>
+        <v>24.16965702159286</v>
       </c>
       <c r="Q10">
-        <v>25.07894958722369</v>
+        <v>24.95765702159286</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07820297100548954</v>
+        <v>0.07847430429307203</v>
       </c>
       <c r="T10">
-        <v>0.5612182381795155</v>
+        <v>0.5659177205075621</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.03342791547927</v>
+        <v>23.14082481375934</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07479128591808096</v>
+        <v>0.07463168827876895</v>
       </c>
       <c r="C11">
-        <v>283.0177054272716</v>
+        <v>280.4292667819602</v>
       </c>
       <c r="D11">
-        <v>283.6877054272716</v>
+        <v>284.3292667819602</v>
       </c>
       <c r="E11">
-        <v>-162.33</v>
+        <v>-159.1</v>
       </c>
       <c r="F11">
-        <v>29.07</v>
+        <v>32.3</v>
       </c>
       <c r="G11">
         <v>28.4</v>
@@ -2189,28 +2189,28 @@
         <v>33.837</v>
       </c>
       <c r="M11">
-        <v>1.462221</v>
+        <v>1.62469</v>
       </c>
       <c r="N11">
-        <v>32.374779</v>
+        <v>32.21231</v>
       </c>
       <c r="O11">
-        <v>8.205121978407146</v>
+        <v>8.163945544037976</v>
       </c>
       <c r="P11">
-        <v>24.16965702159286</v>
+        <v>24.04836445596203</v>
       </c>
       <c r="Q11">
-        <v>24.95765702159286</v>
+        <v>24.83636445596203</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07847430429307203</v>
+        <v>0.07875166720926746</v>
       </c>
       <c r="T11">
-        <v>0.5659177205075621</v>
+        <v>0.5707216357762318</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.14082481375934</v>
+        <v>20.82674233238341</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07463168827876895</v>
+        <v>0.07447209063945694</v>
       </c>
       <c r="C12">
-        <v>280.4292667819602</v>
+        <v>277.8437365032205</v>
       </c>
       <c r="D12">
-        <v>284.3292667819602</v>
+        <v>284.9737365032205</v>
       </c>
       <c r="E12">
-        <v>-159.1</v>
+        <v>-155.87</v>
       </c>
       <c r="F12">
-        <v>32.3</v>
+        <v>35.53</v>
       </c>
       <c r="G12">
         <v>28.4</v>
@@ -2271,28 +2271,28 @@
         <v>33.837</v>
       </c>
       <c r="M12">
-        <v>1.62469</v>
+        <v>1.787159</v>
       </c>
       <c r="N12">
-        <v>32.21231</v>
+        <v>32.049841</v>
       </c>
       <c r="O12">
-        <v>8.163945544037976</v>
+        <v>8.122769109668807</v>
       </c>
       <c r="P12">
-        <v>24.04836445596203</v>
+        <v>23.92707189033119</v>
       </c>
       <c r="Q12">
-        <v>24.83636445596203</v>
+        <v>24.71507189033119</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07875166720926746</v>
+        <v>0.07903526299998415</v>
       </c>
       <c r="T12">
-        <v>0.5707216357762318</v>
+        <v>0.5756335041970064</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.82674233238341</v>
+        <v>18.93340212034855</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07447209063945694</v>
+        <v>0.07431249300014493</v>
       </c>
       <c r="C13">
-        <v>277.8437365032205</v>
+        <v>275.2611344125677</v>
       </c>
       <c r="D13">
-        <v>284.9737365032205</v>
+        <v>285.6211344125678</v>
       </c>
       <c r="E13">
-        <v>-155.87</v>
+        <v>-152.64</v>
       </c>
       <c r="F13">
-        <v>35.53</v>
+        <v>38.76</v>
       </c>
       <c r="G13">
         <v>28.4</v>
@@ -2353,28 +2353,28 @@
         <v>33.837</v>
       </c>
       <c r="M13">
-        <v>1.787159</v>
+        <v>1.949628</v>
       </c>
       <c r="N13">
-        <v>32.049841</v>
+        <v>31.887372</v>
       </c>
       <c r="O13">
-        <v>8.122769109668807</v>
+        <v>8.081592675299639</v>
       </c>
       <c r="P13">
-        <v>23.92707189033119</v>
+        <v>23.80577932470036</v>
       </c>
       <c r="Q13">
-        <v>24.71507189033119</v>
+        <v>24.59377932470036</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07903526299998415</v>
+        <v>0.07932530414958075</v>
       </c>
       <c r="T13">
-        <v>0.5756335041970064</v>
+        <v>0.5806570059909806</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.93340212034855</v>
+        <v>17.35561861031951</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07431249300014493</v>
+        <v>0.07415289536083293</v>
       </c>
       <c r="C14">
-        <v>275.2611344125677</v>
+        <v>272.6814805120483</v>
       </c>
       <c r="D14">
-        <v>285.6211344125678</v>
+        <v>286.2714805120484</v>
       </c>
       <c r="E14">
-        <v>-152.64</v>
+        <v>-149.41</v>
       </c>
       <c r="F14">
-        <v>38.76</v>
+        <v>41.99</v>
       </c>
       <c r="G14">
         <v>28.4</v>
@@ -2435,28 +2435,28 @@
         <v>33.837</v>
       </c>
       <c r="M14">
-        <v>1.949628</v>
+        <v>2.112097</v>
       </c>
       <c r="N14">
-        <v>31.887372</v>
+        <v>31.724903</v>
       </c>
       <c r="O14">
-        <v>8.081592675299639</v>
+        <v>8.040416240930472</v>
       </c>
       <c r="P14">
-        <v>23.80577932470036</v>
+        <v>23.68448675906953</v>
       </c>
       <c r="Q14">
-        <v>24.59377932470036</v>
+        <v>24.47248675906953</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07932530414958075</v>
+        <v>0.07962201291181176</v>
       </c>
       <c r="T14">
-        <v>0.5806570059909806</v>
+        <v>0.5857959905848161</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.35561861031951</v>
+        <v>16.02057102491032</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07415289536083293</v>
+        <v>0.07399329772152091</v>
       </c>
       <c r="C15">
-        <v>272.6814805120483</v>
+        <v>270.1047949862989</v>
       </c>
       <c r="D15">
-        <v>286.2714805120484</v>
+        <v>286.9247949862989</v>
       </c>
       <c r="E15">
-        <v>-149.41</v>
+        <v>-146.18</v>
       </c>
       <c r="F15">
-        <v>41.99</v>
+        <v>45.22000000000001</v>
       </c>
       <c r="G15">
         <v>28.4</v>
@@ -2517,28 +2517,28 @@
         <v>33.837</v>
       </c>
       <c r="M15">
-        <v>2.112097</v>
+        <v>2.274566</v>
       </c>
       <c r="N15">
-        <v>31.724903</v>
+        <v>31.562434</v>
       </c>
       <c r="O15">
-        <v>8.040416240930472</v>
+        <v>7.999239806561303</v>
       </c>
       <c r="P15">
-        <v>23.68448675906953</v>
+        <v>23.5631941934387</v>
       </c>
       <c r="Q15">
-        <v>24.47248675906953</v>
+        <v>24.3511941934387</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07962201291181176</v>
+        <v>0.07992562187781557</v>
       </c>
       <c r="T15">
-        <v>0.5857959905848161</v>
+        <v>0.5910544864482757</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.02057102491032</v>
+        <v>14.87624452313101</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07399329772152091</v>
+        <v>0.07383370008220891</v>
       </c>
       <c r="C16">
-        <v>270.1047949862989</v>
+        <v>267.5310982046352</v>
       </c>
       <c r="D16">
-        <v>286.9247949862989</v>
+        <v>287.5810982046352</v>
       </c>
       <c r="E16">
-        <v>-146.18</v>
+        <v>-142.95</v>
       </c>
       <c r="F16">
-        <v>45.22000000000001</v>
+        <v>48.45000000000001</v>
       </c>
       <c r="G16">
         <v>28.4</v>
@@ -2599,28 +2599,28 @@
         <v>33.837</v>
       </c>
       <c r="M16">
-        <v>2.274566</v>
+        <v>2.437035</v>
       </c>
       <c r="N16">
-        <v>31.562434</v>
+        <v>31.399965</v>
       </c>
       <c r="O16">
-        <v>7.999239806561303</v>
+        <v>7.958063372192134</v>
       </c>
       <c r="P16">
-        <v>23.5631941934387</v>
+        <v>23.44190162780787</v>
       </c>
       <c r="Q16">
-        <v>24.3511941934387</v>
+        <v>24.22990162780787</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07992562187781557</v>
+        <v>0.08023637458419597</v>
       </c>
       <c r="T16">
-        <v>0.5910544864482757</v>
+        <v>0.5964367116261697</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.87624452313101</v>
+        <v>13.8844948882556</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07383370008220889</v>
+        <v>0.0736741024428969</v>
       </c>
       <c r="C17">
-        <v>267.5310982046353</v>
+        <v>264.9604107231689</v>
       </c>
       <c r="D17">
-        <v>287.5810982046353</v>
+        <v>288.240410723169</v>
       </c>
       <c r="E17">
-        <v>-142.95</v>
+        <v>-139.72</v>
       </c>
       <c r="F17">
-        <v>48.45</v>
+        <v>51.68</v>
       </c>
       <c r="G17">
         <v>28.4</v>
@@ -2681,28 +2681,28 @@
         <v>33.837</v>
       </c>
       <c r="M17">
-        <v>2.437035</v>
+        <v>2.599504</v>
       </c>
       <c r="N17">
-        <v>31.399965</v>
+        <v>31.237496</v>
       </c>
       <c r="O17">
-        <v>7.958063372192134</v>
+        <v>7.916886937822967</v>
       </c>
       <c r="P17">
-        <v>23.44190162780787</v>
+        <v>23.32060906217704</v>
       </c>
       <c r="Q17">
-        <v>24.22990162780787</v>
+        <v>24.10860906217704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08023637458419595</v>
+        <v>0.08055452616453779</v>
       </c>
       <c r="T17">
-        <v>0.5964367116261696</v>
+        <v>0.601947085022585</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.88449488825561</v>
+        <v>13.01671395773963</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0736741024428969</v>
+        <v>0.0737048771468372</v>
       </c>
       <c r="C18">
-        <v>264.9604107231689</v>
+        <v>261.6030424317487</v>
       </c>
       <c r="D18">
-        <v>288.240410723169</v>
+        <v>288.1130424317488</v>
       </c>
       <c r="E18">
-        <v>-139.72</v>
+        <v>-136.49</v>
       </c>
       <c r="F18">
-        <v>51.68</v>
+        <v>54.91</v>
       </c>
       <c r="G18">
         <v>28.4</v>
@@ -2763,45 +2763,45 @@
         <v>33.837</v>
       </c>
       <c r="M18">
-        <v>2.599504</v>
+        <v>2.844338</v>
       </c>
       <c r="N18">
-        <v>31.237496</v>
+        <v>30.992662</v>
       </c>
       <c r="O18">
-        <v>7.916886937822967</v>
+        <v>7.854835770324299</v>
       </c>
       <c r="P18">
-        <v>23.32060906217704</v>
+        <v>23.1378262296757</v>
       </c>
       <c r="Q18">
-        <v>24.10860906217704</v>
+        <v>23.9258262296757</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08055452616453779</v>
+        <v>0.08088034404802036</v>
       </c>
       <c r="T18">
-        <v>0.601947085022585</v>
+        <v>0.6075902385008416</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.2534417911673511</v>
       </c>
       <c r="W18">
-        <v>0.03755187790428224</v>
+        <v>0.03867171521753121</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.01671395773963</v>
+        <v>11.89626549306025</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0737048771468372</v>
+        <v>0.07355647788065768</v>
       </c>
       <c r="C19">
-        <v>261.6030424317487</v>
+        <v>258.9882669415559</v>
       </c>
       <c r="D19">
-        <v>288.1130424317488</v>
+        <v>288.7282669415559</v>
       </c>
       <c r="E19">
-        <v>-136.49</v>
+        <v>-133.26</v>
       </c>
       <c r="F19">
-        <v>54.91</v>
+        <v>58.14000000000001</v>
       </c>
       <c r="G19">
         <v>28.4</v>
@@ -2845,28 +2845,28 @@
         <v>33.837</v>
       </c>
       <c r="M19">
-        <v>2.844338</v>
+        <v>3.011652</v>
       </c>
       <c r="N19">
-        <v>30.992662</v>
+        <v>30.825348</v>
       </c>
       <c r="O19">
-        <v>7.854835770324299</v>
+        <v>7.812431410476925</v>
       </c>
       <c r="P19">
-        <v>23.1378262296757</v>
+        <v>23.01291658952308</v>
       </c>
       <c r="Q19">
-        <v>23.9258262296757</v>
+        <v>23.80091658952308</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08088034404802036</v>
+        <v>0.08121410870914887</v>
       </c>
       <c r="T19">
-        <v>0.6075902385008416</v>
+        <v>0.6133710298688118</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.89626549306025</v>
+        <v>11.2353618545569</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07355647788065768</v>
+        <v>0.07340807861447818</v>
       </c>
       <c r="C20">
-        <v>258.9882669415559</v>
+        <v>256.3761245231561</v>
       </c>
       <c r="D20">
-        <v>288.7282669415559</v>
+        <v>289.3461245231561</v>
       </c>
       <c r="E20">
-        <v>-133.26</v>
+        <v>-130.03</v>
       </c>
       <c r="F20">
-        <v>58.14</v>
+        <v>61.37</v>
       </c>
       <c r="G20">
         <v>28.4</v>
@@ -2927,28 +2927,28 @@
         <v>33.837</v>
       </c>
       <c r="M20">
-        <v>3.011652</v>
+        <v>3.178966</v>
       </c>
       <c r="N20">
-        <v>30.82534800000001</v>
+        <v>30.658034</v>
       </c>
       <c r="O20">
-        <v>7.812431410476925</v>
+        <v>7.770027050629551</v>
       </c>
       <c r="P20">
-        <v>23.01291658952308</v>
+        <v>22.88800694937045</v>
       </c>
       <c r="Q20">
-        <v>23.80091658952308</v>
+        <v>23.67600694937045</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08121410870914886</v>
+        <v>0.08155611447302127</v>
       </c>
       <c r="T20">
-        <v>0.6133710298688116</v>
+        <v>0.6192945568261145</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.2353618545569</v>
+        <v>10.64402702010654</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07340807861447818</v>
+        <v>0.07325967934829866</v>
       </c>
       <c r="C21">
-        <v>256.3761245231561</v>
+        <v>253.7666321165486</v>
       </c>
       <c r="D21">
-        <v>289.3461245231561</v>
+        <v>289.9666321165487</v>
       </c>
       <c r="E21">
-        <v>-130.03</v>
+        <v>-126.8</v>
       </c>
       <c r="F21">
-        <v>61.37</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G21">
         <v>28.4</v>
@@ -3009,28 +3009,28 @@
         <v>33.837</v>
       </c>
       <c r="M21">
-        <v>3.178966</v>
+        <v>3.346280000000001</v>
       </c>
       <c r="N21">
-        <v>30.658034</v>
+        <v>30.49072</v>
       </c>
       <c r="O21">
-        <v>7.770027050629551</v>
+        <v>7.727622690782177</v>
       </c>
       <c r="P21">
-        <v>22.88800694937045</v>
+        <v>22.76309730921783</v>
       </c>
       <c r="Q21">
-        <v>23.67600694937045</v>
+        <v>23.55109730921783</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08155611447302127</v>
+        <v>0.08190667038099052</v>
       </c>
       <c r="T21">
-        <v>0.6192945568261145</v>
+        <v>0.6253661719573499</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.64402702010654</v>
+        <v>10.11182566910121</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07325967934829866</v>
+        <v>0.07337780136267238</v>
       </c>
       <c r="C22">
-        <v>253.7666321165486</v>
+        <v>250.0425082330794</v>
       </c>
       <c r="D22">
-        <v>289.9666321165487</v>
+        <v>289.4725082330795</v>
       </c>
       <c r="E22">
-        <v>-126.8</v>
+        <v>-123.57</v>
       </c>
       <c r="F22">
-        <v>64.60000000000001</v>
+        <v>67.83000000000001</v>
       </c>
       <c r="G22">
         <v>28.4</v>
@@ -3091,45 +3091,45 @@
         <v>33.837</v>
       </c>
       <c r="M22">
-        <v>3.346280000000001</v>
+        <v>3.628905</v>
       </c>
       <c r="N22">
-        <v>30.49072</v>
+        <v>30.208095</v>
       </c>
       <c r="O22">
-        <v>7.727622690782177</v>
+        <v>7.655993704553504</v>
       </c>
       <c r="P22">
-        <v>22.76309730921783</v>
+        <v>22.5521012954465</v>
       </c>
       <c r="Q22">
-        <v>23.55109730921783</v>
+        <v>23.3401012954465</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08190667038099052</v>
+        <v>0.08226610112207289</v>
       </c>
       <c r="T22">
-        <v>0.6253661719573499</v>
+        <v>0.6315914988640595</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.2534417911673511</v>
       </c>
       <c r="W22">
-        <v>0.03867171521753121</v>
+        <v>0.03994086417254671</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.11182566910121</v>
+        <v>9.324300305464044</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07337780136267238</v>
+        <v>0.07324209358604301</v>
       </c>
       <c r="C23">
-        <v>250.0425082330794</v>
+        <v>247.3803405669958</v>
       </c>
       <c r="D23">
-        <v>289.4725082330795</v>
+        <v>290.0403405669958</v>
       </c>
       <c r="E23">
-        <v>-123.57</v>
+        <v>-120.34</v>
       </c>
       <c r="F23">
-        <v>67.83</v>
+        <v>71.06</v>
       </c>
       <c r="G23">
         <v>28.4</v>
@@ -3173,28 +3173,28 @@
         <v>33.837</v>
       </c>
       <c r="M23">
-        <v>3.628905</v>
+        <v>3.80171</v>
       </c>
       <c r="N23">
-        <v>30.208095</v>
+        <v>30.03529</v>
       </c>
       <c r="O23">
-        <v>7.655993704553504</v>
+        <v>7.61219769583083</v>
       </c>
       <c r="P23">
-        <v>22.5521012954465</v>
+        <v>22.42309230416917</v>
       </c>
       <c r="Q23">
-        <v>23.3401012954465</v>
+        <v>23.21109230416917</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08226610112207289</v>
+        <v>0.08263474803600351</v>
       </c>
       <c r="T23">
-        <v>0.6315914988640594</v>
+        <v>0.6379764495376078</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.324300305464046</v>
+        <v>8.900468473397499</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07324209358604301</v>
+        <v>0.07310638580941366</v>
       </c>
       <c r="C24">
-        <v>247.3803405669958</v>
+        <v>244.7204050112678</v>
       </c>
       <c r="D24">
-        <v>290.0403405669958</v>
+        <v>290.6104050112678</v>
       </c>
       <c r="E24">
-        <v>-120.34</v>
+        <v>-117.11</v>
       </c>
       <c r="F24">
-        <v>71.06</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G24">
         <v>28.4</v>
@@ -3255,28 +3255,28 @@
         <v>33.837</v>
       </c>
       <c r="M24">
-        <v>3.80171</v>
+        <v>3.974515</v>
       </c>
       <c r="N24">
-        <v>30.03529</v>
+        <v>29.862485</v>
       </c>
       <c r="O24">
-        <v>7.61219769583083</v>
+        <v>7.568401687108156</v>
       </c>
       <c r="P24">
-        <v>22.42309230416917</v>
+        <v>22.29408331289185</v>
       </c>
       <c r="Q24">
-        <v>23.21109230416917</v>
+        <v>23.08208331289185</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08263474803600351</v>
+        <v>0.08301297019445184</v>
       </c>
       <c r="T24">
-        <v>0.6379764495376078</v>
+        <v>0.6445272430857939</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.900468473397499</v>
+        <v>8.513491583249781</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07310638580941366</v>
+        <v>0.0729706780327843</v>
       </c>
       <c r="C25">
-        <v>244.7204050112678</v>
+        <v>242.0627147532261</v>
       </c>
       <c r="D25">
-        <v>290.6104050112678</v>
+        <v>291.1827147532261</v>
       </c>
       <c r="E25">
-        <v>-117.11</v>
+        <v>-113.88</v>
       </c>
       <c r="F25">
-        <v>74.29000000000001</v>
+        <v>77.52000000000001</v>
       </c>
       <c r="G25">
         <v>28.4</v>
@@ -3337,28 +3337,28 @@
         <v>33.837</v>
       </c>
       <c r="M25">
-        <v>3.974515</v>
+        <v>4.147320000000001</v>
       </c>
       <c r="N25">
-        <v>29.862485</v>
+        <v>29.68968</v>
       </c>
       <c r="O25">
-        <v>7.568401687108156</v>
+        <v>7.524605678385481</v>
       </c>
       <c r="P25">
-        <v>22.29408331289185</v>
+        <v>22.16507432161452</v>
       </c>
       <c r="Q25">
-        <v>23.08208331289185</v>
+        <v>22.95307432161452</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08301297019445184</v>
+        <v>0.08340114556759617</v>
       </c>
       <c r="T25">
-        <v>0.6445272430857939</v>
+        <v>0.6512504259378795</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.513491583249781</v>
+        <v>8.15876276728104</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0729706780327843</v>
+        <v>0.07283497025615494</v>
       </c>
       <c r="C26">
-        <v>242.0627147532261</v>
+        <v>239.4072830842876</v>
       </c>
       <c r="D26">
-        <v>291.1827147532261</v>
+        <v>291.7572830842876</v>
       </c>
       <c r="E26">
-        <v>-113.88</v>
+        <v>-110.65</v>
       </c>
       <c r="F26">
-        <v>77.52</v>
+        <v>80.75</v>
       </c>
       <c r="G26">
         <v>28.4</v>
@@ -3419,28 +3419,28 @@
         <v>33.837</v>
       </c>
       <c r="M26">
-        <v>4.14732</v>
+        <v>4.320125</v>
       </c>
       <c r="N26">
-        <v>29.68968</v>
+        <v>29.516875</v>
       </c>
       <c r="O26">
-        <v>7.524605678385481</v>
+        <v>7.480809669662808</v>
       </c>
       <c r="P26">
-        <v>22.16507432161452</v>
+        <v>22.03606533033719</v>
       </c>
       <c r="Q26">
-        <v>22.95307432161452</v>
+        <v>22.82406533033719</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08340114556759617</v>
+        <v>0.08379967228402435</v>
       </c>
       <c r="T26">
-        <v>0.6512504259378795</v>
+        <v>0.6581528936660207</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.15876276728104</v>
+        <v>7.832412256589798</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07283497025615494</v>
+        <v>0.07285454658696276</v>
       </c>
       <c r="C27">
-        <v>239.4072830842876</v>
+        <v>236.0942596377167</v>
       </c>
       <c r="D27">
-        <v>291.7572830842876</v>
+        <v>291.6742596377167</v>
       </c>
       <c r="E27">
-        <v>-110.65</v>
+        <v>-107.42</v>
       </c>
       <c r="F27">
-        <v>80.75</v>
+        <v>83.98</v>
       </c>
       <c r="G27">
         <v>28.4</v>
@@ -3501,45 +3501,45 @@
         <v>33.837</v>
       </c>
       <c r="M27">
-        <v>4.320125</v>
+        <v>4.560114</v>
       </c>
       <c r="N27">
-        <v>29.516875</v>
+        <v>29.276886</v>
       </c>
       <c r="O27">
-        <v>7.480809669662808</v>
+        <v>7.419986427642346</v>
       </c>
       <c r="P27">
-        <v>22.03606533033719</v>
+        <v>21.85689957235766</v>
       </c>
       <c r="Q27">
-        <v>22.82406533033719</v>
+        <v>22.64489957235766</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08379967228402435</v>
+        <v>0.08420896999278842</v>
       </c>
       <c r="T27">
-        <v>0.6581528936660207</v>
+        <v>0.6652419145760036</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.2534417911673511</v>
       </c>
       <c r="W27">
-        <v>0.03994086417254671</v>
+        <v>0.04053811073961284</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.832412256589798</v>
+        <v>7.420209231611316</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07285454658696276</v>
+        <v>0.07272481127600405</v>
       </c>
       <c r="C28">
-        <v>236.0942596377167</v>
+        <v>233.4153513039609</v>
       </c>
       <c r="D28">
-        <v>291.6742596377167</v>
+        <v>292.2253513039609</v>
       </c>
       <c r="E28">
-        <v>-107.42</v>
+        <v>-104.19</v>
       </c>
       <c r="F28">
-        <v>83.98</v>
+        <v>87.21000000000001</v>
       </c>
       <c r="G28">
         <v>28.4</v>
@@ -3583,28 +3583,28 @@
         <v>33.837</v>
       </c>
       <c r="M28">
-        <v>4.560114</v>
+        <v>4.735503</v>
       </c>
       <c r="N28">
-        <v>29.276886</v>
+        <v>29.101497</v>
       </c>
       <c r="O28">
-        <v>7.419986427642346</v>
+        <v>7.375535525331295</v>
       </c>
       <c r="P28">
-        <v>21.85689957235766</v>
+        <v>21.72596147466871</v>
       </c>
       <c r="Q28">
-        <v>22.64489957235766</v>
+        <v>22.51396147466871</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08420896999278842</v>
+        <v>0.08462948133740902</v>
       </c>
       <c r="T28">
-        <v>0.6652419145760036</v>
+        <v>0.6725251552369449</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.420209231611316</v>
+        <v>7.145386667477562</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07272481127600405</v>
+        <v>0.07259507596504536</v>
       </c>
       <c r="C29">
-        <v>233.4153513039609</v>
+        <v>230.7385293862517</v>
       </c>
       <c r="D29">
-        <v>292.2253513039609</v>
+        <v>292.7785293862518</v>
       </c>
       <c r="E29">
-        <v>-104.19</v>
+        <v>-100.96</v>
       </c>
       <c r="F29">
-        <v>87.21000000000001</v>
+        <v>90.44000000000001</v>
       </c>
       <c r="G29">
         <v>28.4</v>
@@ -3665,28 +3665,28 @@
         <v>33.837</v>
       </c>
       <c r="M29">
-        <v>4.735503</v>
+        <v>4.910892</v>
       </c>
       <c r="N29">
-        <v>29.101497</v>
+        <v>28.926108</v>
       </c>
       <c r="O29">
-        <v>7.375535525331295</v>
+        <v>7.331084623020245</v>
       </c>
       <c r="P29">
-        <v>21.72596147466871</v>
+        <v>21.59502337697976</v>
       </c>
       <c r="Q29">
-        <v>22.51396147466871</v>
+        <v>22.38302337697976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08462948133740902</v>
+        <v>0.08506167355271356</v>
       </c>
       <c r="T29">
-        <v>0.6725251552369449</v>
+        <v>0.6800107081384679</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.145386667477562</v>
+        <v>6.890194286496221</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07259507596504536</v>
+        <v>0.07246534065408666</v>
       </c>
       <c r="C30">
-        <v>230.7385293862517</v>
+        <v>228.0638057557213</v>
       </c>
       <c r="D30">
-        <v>292.7785293862518</v>
+        <v>293.3338057557213</v>
       </c>
       <c r="E30">
-        <v>-100.96</v>
+        <v>-97.72999999999999</v>
       </c>
       <c r="F30">
-        <v>90.44000000000001</v>
+        <v>93.67000000000002</v>
       </c>
       <c r="G30">
         <v>28.4</v>
@@ -3747,28 +3747,28 @@
         <v>33.837</v>
       </c>
       <c r="M30">
-        <v>4.910892</v>
+        <v>5.086281000000001</v>
       </c>
       <c r="N30">
-        <v>28.926108</v>
+        <v>28.750719</v>
       </c>
       <c r="O30">
-        <v>7.331084623020245</v>
+        <v>7.286633720709195</v>
       </c>
       <c r="P30">
-        <v>21.59502337697976</v>
+        <v>21.46408527929081</v>
       </c>
       <c r="Q30">
-        <v>22.38302337697976</v>
+        <v>22.25208527929081</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08506167355271356</v>
+        <v>0.08550604019661823</v>
       </c>
       <c r="T30">
-        <v>0.6800107081384679</v>
+        <v>0.6877071216851043</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.890194286496221</v>
+        <v>6.652601380065316</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07246534065408665</v>
+        <v>0.07233560534312794</v>
       </c>
       <c r="C31">
-        <v>228.0638057557213</v>
+        <v>225.3911923737307</v>
       </c>
       <c r="D31">
-        <v>293.3338057557214</v>
+        <v>293.8911923737307</v>
       </c>
       <c r="E31">
-        <v>-97.73000000000002</v>
+        <v>-94.50000000000001</v>
       </c>
       <c r="F31">
-        <v>93.66999999999999</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G31">
         <v>28.4</v>
@@ -3829,28 +3829,28 @@
         <v>33.837</v>
       </c>
       <c r="M31">
-        <v>5.086281</v>
+        <v>5.26167</v>
       </c>
       <c r="N31">
-        <v>28.750719</v>
+        <v>28.57533</v>
       </c>
       <c r="O31">
-        <v>7.286633720709195</v>
+        <v>7.242182818398144</v>
       </c>
       <c r="P31">
-        <v>21.46408527929081</v>
+        <v>21.33314718160186</v>
       </c>
       <c r="Q31">
-        <v>22.25208527929081</v>
+        <v>22.12114718160186</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08550604019661821</v>
+        <v>0.08596310303034871</v>
       </c>
       <c r="T31">
-        <v>0.6877071216851042</v>
+        <v>0.6956234327616445</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.652601380065318</v>
+        <v>6.430848000729807</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07233560534312794</v>
+        <v>0.07220587003216926</v>
       </c>
       <c r="C32">
-        <v>225.3911923737307</v>
+        <v>222.720701292729</v>
       </c>
       <c r="D32">
-        <v>293.8911923737307</v>
+        <v>294.450701292729</v>
       </c>
       <c r="E32">
-        <v>-94.50000000000001</v>
+        <v>-91.27000000000001</v>
       </c>
       <c r="F32">
-        <v>96.89999999999999</v>
+        <v>100.13</v>
       </c>
       <c r="G32">
         <v>28.4</v>
@@ -3911,28 +3911,28 @@
         <v>33.837</v>
       </c>
       <c r="M32">
-        <v>5.26167</v>
+        <v>5.437059</v>
       </c>
       <c r="N32">
-        <v>28.57533</v>
+        <v>28.39994100000001</v>
       </c>
       <c r="O32">
-        <v>7.242182818398144</v>
+        <v>7.197731916087094</v>
       </c>
       <c r="P32">
-        <v>21.33314718160186</v>
+        <v>21.20220908391291</v>
       </c>
       <c r="Q32">
-        <v>22.12114718160186</v>
+        <v>21.99020908391291</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08596310303034871</v>
+        <v>0.08643341406215838</v>
       </c>
       <c r="T32">
-        <v>0.6956234327616445</v>
+        <v>0.7037692021302584</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.430848000729807</v>
+        <v>6.223401291028846</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07220587003216926</v>
+        <v>0.07231503334803698</v>
       </c>
       <c r="C33">
-        <v>222.720701292729</v>
+        <v>219.0197712330652</v>
       </c>
       <c r="D33">
-        <v>294.450701292729</v>
+        <v>293.9797712330652</v>
       </c>
       <c r="E33">
-        <v>-91.27000000000001</v>
+        <v>-88.04000000000001</v>
       </c>
       <c r="F33">
-        <v>100.13</v>
+        <v>103.36</v>
       </c>
       <c r="G33">
         <v>28.4</v>
@@ -3993,45 +3993,45 @@
         <v>33.837</v>
       </c>
       <c r="M33">
-        <v>5.437059</v>
+        <v>5.715808</v>
       </c>
       <c r="N33">
-        <v>28.39994100000001</v>
+        <v>28.121192</v>
       </c>
       <c r="O33">
-        <v>7.197731916087094</v>
+        <v>7.127085270240985</v>
       </c>
       <c r="P33">
-        <v>21.20220908391291</v>
+        <v>20.99410672975902</v>
       </c>
       <c r="Q33">
-        <v>21.99020908391291</v>
+        <v>21.78210672975902</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08643341406215838</v>
+        <v>0.08691755777137417</v>
       </c>
       <c r="T33">
-        <v>0.7037692021302584</v>
+        <v>0.7121545529508903</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.2534417911673511</v>
       </c>
       <c r="W33">
-        <v>0.04053811073961284</v>
+        <v>0.04128466894844549</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.223401291028846</v>
+        <v>5.919897939189001</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07231503334803698</v>
+        <v>0.07219276361916661</v>
       </c>
       <c r="C34">
-        <v>219.0197712330652</v>
+        <v>216.3173437680001</v>
       </c>
       <c r="D34">
-        <v>293.9797712330652</v>
+        <v>294.5073437680002</v>
       </c>
       <c r="E34">
-        <v>-88.04000000000001</v>
+        <v>-84.81</v>
       </c>
       <c r="F34">
-        <v>103.36</v>
+        <v>106.59</v>
       </c>
       <c r="G34">
         <v>28.4</v>
@@ -4075,28 +4075,28 @@
         <v>33.837</v>
       </c>
       <c r="M34">
-        <v>5.715808</v>
+        <v>5.894427</v>
       </c>
       <c r="N34">
-        <v>28.121192</v>
+        <v>27.942573</v>
       </c>
       <c r="O34">
-        <v>7.127085270240985</v>
+        <v>7.081815750944465</v>
       </c>
       <c r="P34">
-        <v>20.99410672975902</v>
+        <v>20.86075724905554</v>
       </c>
       <c r="Q34">
-        <v>21.78210672975902</v>
+        <v>21.64875724905554</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08691755777137417</v>
+        <v>0.08741615353161136</v>
       </c>
       <c r="T34">
-        <v>0.7121545529508903</v>
+        <v>0.7207902127512426</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.919897939189001</v>
+        <v>5.74050709254691</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07219276361916661</v>
+        <v>0.07207049389029624</v>
       </c>
       <c r="C35">
-        <v>216.3173437680001</v>
+        <v>213.6168132577432</v>
       </c>
       <c r="D35">
-        <v>294.5073437680002</v>
+        <v>295.0368132577432</v>
       </c>
       <c r="E35">
-        <v>-84.81</v>
+        <v>-81.58</v>
       </c>
       <c r="F35">
-        <v>106.59</v>
+        <v>109.82</v>
       </c>
       <c r="G35">
         <v>28.4</v>
@@ -4157,28 +4157,28 @@
         <v>33.837</v>
       </c>
       <c r="M35">
-        <v>5.894427</v>
+        <v>6.073046000000001</v>
       </c>
       <c r="N35">
-        <v>27.942573</v>
+        <v>27.763954</v>
       </c>
       <c r="O35">
-        <v>7.081815750944465</v>
+        <v>7.036546231647943</v>
       </c>
       <c r="P35">
-        <v>20.86075724905554</v>
+        <v>20.72740776835206</v>
       </c>
       <c r="Q35">
-        <v>21.64875724905554</v>
+        <v>21.51540776835206</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08741615353161136</v>
+        <v>0.08792985825427997</v>
       </c>
       <c r="T35">
-        <v>0.7207902127512426</v>
+        <v>0.7296875592122116</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.74050709254691</v>
+        <v>5.571668648648471</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07207049389029624</v>
+        <v>0.07194822416142586</v>
       </c>
       <c r="C36">
-        <v>213.6168132577432</v>
+        <v>210.9181899518379</v>
       </c>
       <c r="D36">
-        <v>295.0368132577432</v>
+        <v>295.5681899518379</v>
       </c>
       <c r="E36">
-        <v>-81.58</v>
+        <v>-78.34999999999999</v>
       </c>
       <c r="F36">
-        <v>109.82</v>
+        <v>113.05</v>
       </c>
       <c r="G36">
         <v>28.4</v>
@@ -4239,28 +4239,28 @@
         <v>33.837</v>
       </c>
       <c r="M36">
-        <v>6.073046000000001</v>
+        <v>6.251665000000001</v>
       </c>
       <c r="N36">
-        <v>27.763954</v>
+        <v>27.585335</v>
       </c>
       <c r="O36">
-        <v>7.036546231647943</v>
+        <v>6.991276712351421</v>
       </c>
       <c r="P36">
-        <v>20.72740776835206</v>
+        <v>20.59405828764858</v>
       </c>
       <c r="Q36">
-        <v>21.51540776835206</v>
+        <v>21.38205828764858</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08792985825427997</v>
+        <v>0.08845936927610762</v>
       </c>
       <c r="T36">
-        <v>0.7296875592122116</v>
+        <v>0.738858670179672</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.571668648648471</v>
+        <v>5.412478115829942</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07194822416142586</v>
+        <v>0.07182595443255549</v>
       </c>
       <c r="C37">
-        <v>210.9181899518379</v>
+        <v>208.2214841738011</v>
       </c>
       <c r="D37">
-        <v>295.5681899518379</v>
+        <v>296.1014841738011</v>
       </c>
       <c r="E37">
-        <v>-78.34999999999999</v>
+        <v>-75.11999999999999</v>
       </c>
       <c r="F37">
-        <v>113.05</v>
+        <v>116.28</v>
       </c>
       <c r="G37">
         <v>28.4</v>
@@ -4321,28 +4321,28 @@
         <v>33.837</v>
       </c>
       <c r="M37">
-        <v>6.251665000000001</v>
+        <v>6.430284000000001</v>
       </c>
       <c r="N37">
-        <v>27.585335</v>
+        <v>27.406716</v>
       </c>
       <c r="O37">
-        <v>6.991276712351421</v>
+        <v>6.946007193054901</v>
       </c>
       <c r="P37">
-        <v>20.59405828764858</v>
+        <v>20.4607088069451</v>
       </c>
       <c r="Q37">
-        <v>21.38205828764858</v>
+        <v>21.2487088069451</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08845936927610762</v>
+        <v>0.08900542751736737</v>
       </c>
       <c r="T37">
-        <v>0.738858670179672</v>
+        <v>0.7483163783648654</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.412478115829942</v>
+        <v>5.262131501501333</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07182595443255549</v>
+        <v>0.07170368470368511</v>
       </c>
       <c r="C38">
-        <v>208.2214841738011</v>
+        <v>205.5267063217914</v>
       </c>
       <c r="D38">
-        <v>296.1014841738011</v>
+        <v>296.6367063217915</v>
       </c>
       <c r="E38">
-        <v>-75.12</v>
+        <v>-71.89</v>
       </c>
       <c r="F38">
-        <v>116.28</v>
+        <v>119.51</v>
       </c>
       <c r="G38">
         <v>28.4</v>
@@ -4403,28 +4403,28 @@
         <v>33.837</v>
       </c>
       <c r="M38">
-        <v>6.430284</v>
+        <v>6.608903000000001</v>
       </c>
       <c r="N38">
-        <v>27.406716</v>
+        <v>27.228097</v>
       </c>
       <c r="O38">
-        <v>6.946007193054901</v>
+        <v>6.900737673758379</v>
       </c>
       <c r="P38">
-        <v>20.4607088069451</v>
+        <v>20.32735932624162</v>
       </c>
       <c r="Q38">
-        <v>21.2487088069451</v>
+        <v>21.11535932624162</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08900542751736737</v>
+        <v>0.08956882094088935</v>
       </c>
       <c r="T38">
-        <v>0.7483163783648654</v>
+        <v>0.7580743312543509</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.262131501501334</v>
+        <v>5.119911731190486</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07170368470368511</v>
+        <v>0.07158141497481474</v>
       </c>
       <c r="C39">
-        <v>205.5267063217914</v>
+        <v>202.8338668692846</v>
       </c>
       <c r="D39">
-        <v>296.6367063217915</v>
+        <v>297.1738668692847</v>
       </c>
       <c r="E39">
-        <v>-71.89</v>
+        <v>-68.66000000000001</v>
       </c>
       <c r="F39">
-        <v>119.51</v>
+        <v>122.74</v>
       </c>
       <c r="G39">
         <v>28.4</v>
@@ -4485,28 +4485,28 @@
         <v>33.837</v>
       </c>
       <c r="M39">
-        <v>6.608903000000001</v>
+        <v>6.787522</v>
       </c>
       <c r="N39">
-        <v>27.228097</v>
+        <v>27.049478</v>
       </c>
       <c r="O39">
-        <v>6.900737673758379</v>
+        <v>6.855468154461859</v>
       </c>
       <c r="P39">
-        <v>20.32735932624162</v>
+        <v>20.19400984553814</v>
       </c>
       <c r="Q39">
-        <v>21.11535932624162</v>
+        <v>20.98200984553814</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08956882094088935</v>
+        <v>0.09015038834581524</v>
       </c>
       <c r="T39">
-        <v>0.7580743312543509</v>
+        <v>0.7681470568176905</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.119911731190486</v>
+        <v>4.985177211948632</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07158141497481474</v>
+        <v>0.07145914524594436</v>
       </c>
       <c r="C40">
-        <v>202.8338668692846</v>
+        <v>200.1429763657574</v>
       </c>
       <c r="D40">
-        <v>297.1738668692847</v>
+        <v>297.7129763657574</v>
       </c>
       <c r="E40">
-        <v>-68.66000000000001</v>
+        <v>-65.43000000000001</v>
       </c>
       <c r="F40">
-        <v>122.74</v>
+        <v>125.97</v>
       </c>
       <c r="G40">
         <v>28.4</v>
@@ -4567,28 +4567,28 @@
         <v>33.837</v>
       </c>
       <c r="M40">
-        <v>6.787522</v>
+        <v>6.966141</v>
       </c>
       <c r="N40">
-        <v>27.049478</v>
+        <v>26.870859</v>
       </c>
       <c r="O40">
-        <v>6.855468154461859</v>
+        <v>6.810198635165338</v>
       </c>
       <c r="P40">
-        <v>20.19400984553814</v>
+        <v>20.06066036483466</v>
       </c>
       <c r="Q40">
-        <v>20.98200984553814</v>
+        <v>20.84866036483466</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09015038834581524</v>
+        <v>0.09075102353450923</v>
       </c>
       <c r="T40">
-        <v>0.7681470568176905</v>
+        <v>0.778550035678189</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.985177211948632</v>
+        <v>4.857352155232</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07145914524594436</v>
+        <v>0.07133687551707399</v>
       </c>
       <c r="C41">
-        <v>200.1429763657574</v>
+        <v>197.4540454373775</v>
       </c>
       <c r="D41">
-        <v>297.7129763657574</v>
+        <v>298.2540454373775</v>
       </c>
       <c r="E41">
-        <v>-65.43000000000001</v>
+        <v>-62.19999999999999</v>
       </c>
       <c r="F41">
-        <v>125.97</v>
+        <v>129.2</v>
       </c>
       <c r="G41">
         <v>28.4</v>
@@ -4649,28 +4649,28 @@
         <v>33.837</v>
       </c>
       <c r="M41">
-        <v>6.966141</v>
+        <v>7.144760000000002</v>
       </c>
       <c r="N41">
-        <v>26.870859</v>
+        <v>26.69224</v>
       </c>
       <c r="O41">
-        <v>6.810198635165338</v>
+        <v>6.764929115868816</v>
       </c>
       <c r="P41">
-        <v>20.06066036483466</v>
+        <v>19.92731088413118</v>
       </c>
       <c r="Q41">
-        <v>20.84866036483466</v>
+        <v>20.71531088413118</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09075102353450923</v>
+        <v>0.09137167989615966</v>
       </c>
       <c r="T41">
-        <v>0.778550035678189</v>
+        <v>0.789299780500704</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.857352155232</v>
+        <v>4.7359183513512</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07133687551707399</v>
+        <v>0.07121460578820361</v>
       </c>
       <c r="C42">
-        <v>197.4540454373775</v>
+        <v>194.7670847877021</v>
       </c>
       <c r="D42">
-        <v>298.2540454373775</v>
+        <v>298.7970847877021</v>
       </c>
       <c r="E42">
-        <v>-62.19999999999999</v>
+        <v>-58.97</v>
       </c>
       <c r="F42">
-        <v>129.2</v>
+        <v>132.43</v>
       </c>
       <c r="G42">
         <v>28.4</v>
@@ -4731,28 +4731,28 @@
         <v>33.837</v>
       </c>
       <c r="M42">
-        <v>7.144760000000002</v>
+        <v>7.323379000000001</v>
       </c>
       <c r="N42">
-        <v>26.69224</v>
+        <v>26.513621</v>
       </c>
       <c r="O42">
-        <v>6.764929115868816</v>
+        <v>6.719659596572295</v>
       </c>
       <c r="P42">
-        <v>19.92731088413118</v>
+        <v>19.7939614034277</v>
       </c>
       <c r="Q42">
-        <v>20.71531088413118</v>
+        <v>20.58196140342771</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09137167989615966</v>
+        <v>0.09201337545651012</v>
       </c>
       <c r="T42">
-        <v>0.789299780500704</v>
+        <v>0.8004139234527958</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.7359183513512</v>
+        <v>4.620408147659707</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07121460578820361</v>
+        <v>0.07109233605933324</v>
       </c>
       <c r="C43">
-        <v>194.7670847877021</v>
+        <v>192.0821051983836</v>
       </c>
       <c r="D43">
-        <v>298.7970847877021</v>
+        <v>299.3421051983836</v>
       </c>
       <c r="E43">
-        <v>-58.97</v>
+        <v>-55.73999999999998</v>
       </c>
       <c r="F43">
-        <v>132.43</v>
+        <v>135.66</v>
       </c>
       <c r="G43">
         <v>28.4</v>
@@ -4813,28 +4813,28 @@
         <v>33.837</v>
       </c>
       <c r="M43">
-        <v>7.323379000000001</v>
+        <v>7.501998000000001</v>
       </c>
       <c r="N43">
-        <v>26.513621</v>
+        <v>26.335002</v>
       </c>
       <c r="O43">
-        <v>6.719659596572295</v>
+        <v>6.674390077275774</v>
       </c>
       <c r="P43">
-        <v>19.7939614034277</v>
+        <v>19.66061192272423</v>
       </c>
       <c r="Q43">
-        <v>20.58196140342771</v>
+        <v>20.44861192272423</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09201337545651012</v>
+        <v>0.0926771984499761</v>
       </c>
       <c r="T43">
-        <v>0.8004139234527958</v>
+        <v>0.8119113127135805</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.620408147659707</v>
+        <v>4.510398429858286</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07109233605933324</v>
+        <v>0.07177261640495795</v>
       </c>
       <c r="C44">
-        <v>192.0821051983836</v>
+        <v>185.8447277753255</v>
       </c>
       <c r="D44">
-        <v>299.3421051983836</v>
+        <v>296.3347277753255</v>
       </c>
       <c r="E44">
-        <v>-55.74000000000001</v>
+        <v>-52.51000000000002</v>
       </c>
       <c r="F44">
-        <v>135.66</v>
+        <v>138.89</v>
       </c>
       <c r="G44">
         <v>28.4</v>
@@ -4895,45 +4895,45 @@
         <v>33.837</v>
       </c>
       <c r="M44">
-        <v>7.501998</v>
+        <v>8.027842</v>
       </c>
       <c r="N44">
-        <v>26.335002</v>
+        <v>25.809158</v>
       </c>
       <c r="O44">
-        <v>6.674390077275774</v>
+        <v>6.54111923204117</v>
       </c>
       <c r="P44">
-        <v>19.66061192272423</v>
+        <v>19.26803876795883</v>
       </c>
       <c r="Q44">
-        <v>20.44861192272423</v>
+        <v>20.05603876795884</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09267719844997609</v>
+        <v>0.09336431347830051</v>
       </c>
       <c r="T44">
-        <v>0.8119113127135804</v>
+        <v>0.8238121191414101</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.2534417911673511</v>
       </c>
       <c r="W44">
-        <v>0.04128466894844549</v>
+        <v>0.04315106447052711</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.510398429858286</v>
+        <v>4.214955899729965</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07177261640495795</v>
+        <v>0.0716690106313084</v>
       </c>
       <c r="C45">
-        <v>185.8447277753255</v>
+        <v>183.0688405591634</v>
       </c>
       <c r="D45">
-        <v>296.3347277753255</v>
+        <v>296.7888405591635</v>
       </c>
       <c r="E45">
-        <v>-52.51000000000002</v>
+        <v>-49.28</v>
       </c>
       <c r="F45">
-        <v>138.89</v>
+        <v>142.12</v>
       </c>
       <c r="G45">
         <v>28.4</v>
@@ -4977,28 +4977,28 @@
         <v>33.837</v>
       </c>
       <c r="M45">
-        <v>8.027842</v>
+        <v>8.214536000000001</v>
       </c>
       <c r="N45">
-        <v>25.809158</v>
+        <v>25.622464</v>
       </c>
       <c r="O45">
-        <v>6.54111923204117</v>
+        <v>6.493803170280972</v>
       </c>
       <c r="P45">
-        <v>19.26803876795883</v>
+        <v>19.12866082971903</v>
       </c>
       <c r="Q45">
-        <v>20.05603876795884</v>
+        <v>19.91666082971903</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09336431347830051</v>
+        <v>0.09407596832906512</v>
       </c>
       <c r="T45">
-        <v>0.8238121191414101</v>
+        <v>0.8361379543702336</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.214955899729965</v>
+        <v>4.119161447463375</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0716690106313084</v>
+        <v>0.07156540485765883</v>
       </c>
       <c r="C46">
-        <v>183.0688405591634</v>
+        <v>180.2943472729178</v>
       </c>
       <c r="D46">
-        <v>296.7888405591635</v>
+        <v>297.2443472729178</v>
       </c>
       <c r="E46">
-        <v>-49.28</v>
+        <v>-46.05000000000001</v>
       </c>
       <c r="F46">
-        <v>142.12</v>
+        <v>145.35</v>
       </c>
       <c r="G46">
         <v>28.4</v>
@@ -5059,28 +5059,28 @@
         <v>33.837</v>
       </c>
       <c r="M46">
-        <v>8.214536000000001</v>
+        <v>8.40123</v>
       </c>
       <c r="N46">
-        <v>25.622464</v>
+        <v>25.43577000000001</v>
       </c>
       <c r="O46">
-        <v>6.493803170280972</v>
+        <v>6.446487108520776</v>
       </c>
       <c r="P46">
-        <v>19.12866082971903</v>
+        <v>18.98928289147923</v>
       </c>
       <c r="Q46">
-        <v>19.91666082971903</v>
+        <v>19.77728289147923</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09407596832906512</v>
+        <v>0.09481350153803933</v>
       </c>
       <c r="T46">
-        <v>0.8361379543702336</v>
+        <v>0.8489120017891963</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.119161447463375</v>
+        <v>4.027624526408633</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07156540485765883</v>
+        <v>0.07266375780022985</v>
       </c>
       <c r="C47">
-        <v>180.2943472729178</v>
+        <v>172.3054164502695</v>
       </c>
       <c r="D47">
-        <v>297.2443472729178</v>
+        <v>292.4854164502696</v>
       </c>
       <c r="E47">
-        <v>-46.05000000000001</v>
+        <v>-42.81999999999999</v>
       </c>
       <c r="F47">
-        <v>145.35</v>
+        <v>148.58</v>
       </c>
       <c r="G47">
         <v>28.4</v>
@@ -5141,45 +5141,45 @@
         <v>33.837</v>
       </c>
       <c r="M47">
-        <v>8.40123</v>
+        <v>9.107954000000001</v>
       </c>
       <c r="N47">
-        <v>25.43577000000001</v>
+        <v>24.729046</v>
       </c>
       <c r="O47">
-        <v>6.446487108520776</v>
+        <v>6.26737371209982</v>
       </c>
       <c r="P47">
-        <v>18.98928289147923</v>
+        <v>18.46167228790019</v>
       </c>
       <c r="Q47">
-        <v>19.77728289147923</v>
+        <v>19.24967228790019</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09481350153803933</v>
+        <v>0.09557835079179039</v>
       </c>
       <c r="T47">
-        <v>0.8489120017891963</v>
+        <v>0.8621591620755281</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.2534417911673511</v>
       </c>
       <c r="W47">
-        <v>0.04315106447052711</v>
+        <v>0.04576401820144137</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.027624526408633</v>
+        <v>3.715104402152229</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07266375780022985</v>
+        <v>0.07258628156388942</v>
       </c>
       <c r="C48">
-        <v>172.3054164502695</v>
+        <v>169.4061036177957</v>
       </c>
       <c r="D48">
-        <v>292.4854164502696</v>
+        <v>292.8161036177957</v>
       </c>
       <c r="E48">
-        <v>-42.81999999999999</v>
+        <v>-39.59</v>
       </c>
       <c r="F48">
-        <v>148.58</v>
+        <v>151.81</v>
       </c>
       <c r="G48">
         <v>28.4</v>
@@ -5223,28 +5223,28 @@
         <v>33.837</v>
       </c>
       <c r="M48">
-        <v>9.107954000000001</v>
+        <v>9.305953000000001</v>
       </c>
       <c r="N48">
-        <v>24.729046</v>
+        <v>24.531047</v>
       </c>
       <c r="O48">
-        <v>6.26737371209982</v>
+        <v>6.217192490890475</v>
       </c>
       <c r="P48">
-        <v>18.46167228790019</v>
+        <v>18.31385450910953</v>
       </c>
       <c r="Q48">
-        <v>19.24967228790019</v>
+        <v>19.10185450910953</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09557835079179039</v>
+        <v>0.09637206228153203</v>
       </c>
       <c r="T48">
-        <v>0.8621591620755281</v>
+        <v>0.8759062152028534</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.715104402152229</v>
+        <v>3.636059627638351</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07258628156388942</v>
+        <v>0.07250880532754901</v>
       </c>
       <c r="C49">
-        <v>169.4061036177957</v>
+        <v>166.5075393886596</v>
       </c>
       <c r="D49">
-        <v>292.8161036177957</v>
+        <v>293.1475393886597</v>
       </c>
       <c r="E49">
-        <v>-39.59</v>
+        <v>-36.35999999999999</v>
       </c>
       <c r="F49">
-        <v>151.81</v>
+        <v>155.04</v>
       </c>
       <c r="G49">
         <v>28.4</v>
@@ -5305,28 +5305,28 @@
         <v>33.837</v>
       </c>
       <c r="M49">
-        <v>9.305953000000001</v>
+        <v>9.503952000000002</v>
       </c>
       <c r="N49">
-        <v>24.531047</v>
+        <v>24.333048</v>
       </c>
       <c r="O49">
-        <v>6.217192490890475</v>
+        <v>6.167011269681131</v>
       </c>
       <c r="P49">
-        <v>18.31385450910953</v>
+        <v>18.16603673031887</v>
       </c>
       <c r="Q49">
-        <v>19.10185450910953</v>
+        <v>18.95403673031887</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09637206228153203</v>
+        <v>0.09719630113626374</v>
       </c>
       <c r="T49">
-        <v>0.8759062152028534</v>
+        <v>0.8901820011427681</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.636059627638351</v>
+        <v>3.560308385395885</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.072508805327549</v>
+        <v>0.07345560695372699</v>
       </c>
       <c r="C50">
-        <v>166.5075393886597</v>
+        <v>159.2779535304527</v>
       </c>
       <c r="D50">
-        <v>293.1475393886597</v>
+        <v>289.1479535304527</v>
       </c>
       <c r="E50">
-        <v>-36.36000000000001</v>
+        <v>-33.13</v>
       </c>
       <c r="F50">
-        <v>155.04</v>
+        <v>158.27</v>
       </c>
       <c r="G50">
         <v>28.4</v>
@@ -5387,45 +5387,45 @@
         <v>33.837</v>
       </c>
       <c r="M50">
-        <v>9.503952</v>
+        <v>10.145107</v>
       </c>
       <c r="N50">
-        <v>24.33304800000001</v>
+        <v>23.691893</v>
       </c>
       <c r="O50">
-        <v>6.167011269681132</v>
+        <v>6.004515798065228</v>
       </c>
       <c r="P50">
-        <v>18.16603673031887</v>
+        <v>17.68737720193477</v>
       </c>
       <c r="Q50">
-        <v>18.95403673031887</v>
+        <v>18.47537720193477</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09719630113626374</v>
+        <v>0.09805286308333788</v>
       </c>
       <c r="T50">
-        <v>0.8901820011427681</v>
+        <v>0.9050176218254246</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.2534417911673511</v>
       </c>
       <c r="W50">
-        <v>0.04576401820144137</v>
+        <v>0.04785438118617279</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.560308385395886</v>
+        <v>3.335302427071493</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07345560695372699</v>
+        <v>0.07339903434723388</v>
       </c>
       <c r="C51">
-        <v>159.2779535304527</v>
+        <v>156.2838656639258</v>
       </c>
       <c r="D51">
-        <v>289.1479535304527</v>
+        <v>289.3838656639259</v>
       </c>
       <c r="E51">
-        <v>-33.13</v>
+        <v>-29.90000000000001</v>
       </c>
       <c r="F51">
-        <v>158.27</v>
+        <v>161.5</v>
       </c>
       <c r="G51">
         <v>28.4</v>
@@ -5469,28 +5469,28 @@
         <v>33.837</v>
       </c>
       <c r="M51">
-        <v>10.145107</v>
+        <v>10.35215</v>
       </c>
       <c r="N51">
-        <v>23.691893</v>
+        <v>23.48485</v>
       </c>
       <c r="O51">
-        <v>6.004515798065228</v>
+        <v>5.952042449296566</v>
       </c>
       <c r="P51">
-        <v>17.68737720193477</v>
+        <v>17.53280755070343</v>
       </c>
       <c r="Q51">
-        <v>18.47537720193477</v>
+        <v>18.32080755070344</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09805286308333788</v>
+        <v>0.09894368750829496</v>
       </c>
       <c r="T51">
-        <v>0.9050176218254246</v>
+        <v>0.9204466673353873</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.335302427071493</v>
+        <v>3.268596378530064</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07339903434723388</v>
+        <v>0.07334246174074077</v>
       </c>
       <c r="C52">
-        <v>156.2838656639258</v>
+        <v>153.2901630671472</v>
       </c>
       <c r="D52">
-        <v>289.3838656639259</v>
+        <v>289.6201630671472</v>
       </c>
       <c r="E52">
-        <v>-29.90000000000001</v>
+        <v>-26.67000000000002</v>
       </c>
       <c r="F52">
-        <v>161.5</v>
+        <v>164.73</v>
       </c>
       <c r="G52">
         <v>28.4</v>
@@ -5551,28 +5551,28 @@
         <v>33.837</v>
       </c>
       <c r="M52">
-        <v>10.35215</v>
+        <v>10.559193</v>
       </c>
       <c r="N52">
-        <v>23.48485</v>
+        <v>23.277807</v>
       </c>
       <c r="O52">
-        <v>5.952042449296566</v>
+        <v>5.899569100527905</v>
       </c>
       <c r="P52">
-        <v>17.53280755070343</v>
+        <v>17.3782378994721</v>
       </c>
       <c r="Q52">
-        <v>18.32080755070344</v>
+        <v>18.1662378994721</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09894368750829496</v>
+        <v>0.09987087211386256</v>
       </c>
       <c r="T52">
-        <v>0.9204466673353873</v>
+        <v>0.9365054698049403</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.268596378530064</v>
+        <v>3.204506253460847</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07334246174074077</v>
+        <v>0.07328588913424768</v>
       </c>
       <c r="C53">
-        <v>153.2901630671472</v>
+        <v>150.2968466846681</v>
       </c>
       <c r="D53">
-        <v>289.6201630671472</v>
+        <v>289.8568466846681</v>
       </c>
       <c r="E53">
-        <v>-26.67000000000002</v>
+        <v>-23.44</v>
       </c>
       <c r="F53">
-        <v>164.73</v>
+        <v>167.96</v>
       </c>
       <c r="G53">
         <v>28.4</v>
@@ -5633,28 +5633,28 @@
         <v>33.837</v>
       </c>
       <c r="M53">
-        <v>10.559193</v>
+        <v>10.766236</v>
       </c>
       <c r="N53">
-        <v>23.277807</v>
+        <v>23.070764</v>
       </c>
       <c r="O53">
-        <v>5.899569100527905</v>
+        <v>5.847095751759243</v>
       </c>
       <c r="P53">
-        <v>17.3782378994721</v>
+        <v>17.22366824824076</v>
       </c>
       <c r="Q53">
-        <v>18.1662378994721</v>
+        <v>18.01166824824076</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09987087211386256</v>
+        <v>0.1008366894113288</v>
       </c>
       <c r="T53">
-        <v>0.9365054698049403</v>
+        <v>0.9532333890440582</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.204506253460847</v>
+        <v>3.142881133201985</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07328588913424768</v>
+        <v>0.07322931652775456</v>
       </c>
       <c r="C54">
-        <v>150.2968466846681</v>
+        <v>147.3039174641301</v>
       </c>
       <c r="D54">
-        <v>289.8568466846681</v>
+        <v>290.0939174641301</v>
       </c>
       <c r="E54">
-        <v>-23.44</v>
+        <v>-20.21000000000001</v>
       </c>
       <c r="F54">
-        <v>167.96</v>
+        <v>171.19</v>
       </c>
       <c r="G54">
         <v>28.4</v>
@@ -5715,28 +5715,28 @@
         <v>33.837</v>
       </c>
       <c r="M54">
-        <v>10.766236</v>
+        <v>10.973279</v>
       </c>
       <c r="N54">
-        <v>23.070764</v>
+        <v>22.86372100000001</v>
       </c>
       <c r="O54">
-        <v>5.847095751759243</v>
+        <v>5.794622402990582</v>
       </c>
       <c r="P54">
-        <v>17.22366824824076</v>
+        <v>17.06909859700942</v>
       </c>
       <c r="Q54">
-        <v>18.01166824824076</v>
+        <v>17.85709859700942</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1008366894113288</v>
+        <v>0.1018436053171979</v>
       </c>
       <c r="T54">
-        <v>0.9532333890440582</v>
+        <v>0.9706731346337767</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.142881133201985</v>
+        <v>3.083581489179306</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07322931652775456</v>
+        <v>0.07317274392126147</v>
       </c>
       <c r="C55">
-        <v>147.3039174641301</v>
+        <v>144.3113763562773</v>
       </c>
       <c r="D55">
-        <v>290.0939174641301</v>
+        <v>290.3313763562774</v>
       </c>
       <c r="E55">
-        <v>-20.21000000000001</v>
+        <v>-16.97999999999999</v>
       </c>
       <c r="F55">
-        <v>171.19</v>
+        <v>174.42</v>
       </c>
       <c r="G55">
         <v>28.4</v>
@@ -5797,28 +5797,28 @@
         <v>33.837</v>
       </c>
       <c r="M55">
-        <v>10.973279</v>
+        <v>11.180322</v>
       </c>
       <c r="N55">
-        <v>22.86372100000001</v>
+        <v>22.656678</v>
       </c>
       <c r="O55">
-        <v>5.794622402990582</v>
+        <v>5.742149054221918</v>
       </c>
       <c r="P55">
-        <v>17.06909859700942</v>
+        <v>16.91452894577808</v>
       </c>
       <c r="Q55">
-        <v>17.85709859700942</v>
+        <v>17.70252894577808</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1018436053171979</v>
+        <v>0.102894300175496</v>
       </c>
       <c r="T55">
-        <v>0.9706731346337767</v>
+        <v>0.9888711300317439</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.083581489179306</v>
+        <v>3.026478128268577</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07317274392126147</v>
+        <v>0.07631890603066044</v>
       </c>
       <c r="C56">
-        <v>144.3113763562773</v>
+        <v>128.4402616580324</v>
       </c>
       <c r="D56">
-        <v>290.3313763562774</v>
+        <v>277.6902616580325</v>
       </c>
       <c r="E56">
-        <v>-16.97999999999999</v>
+        <v>-13.75</v>
       </c>
       <c r="F56">
-        <v>174.42</v>
+        <v>177.65</v>
       </c>
       <c r="G56">
         <v>28.4</v>
@@ -5879,45 +5879,45 @@
         <v>33.837</v>
       </c>
       <c r="M56">
-        <v>11.180322</v>
+        <v>12.773035</v>
       </c>
       <c r="N56">
-        <v>22.656678</v>
+        <v>21.063965</v>
       </c>
       <c r="O56">
-        <v>5.742149054221918</v>
+        <v>5.338489018686394</v>
       </c>
       <c r="P56">
-        <v>16.91452894577808</v>
+        <v>15.72547598131361</v>
       </c>
       <c r="Q56">
-        <v>17.70252894577808</v>
+        <v>16.51347598131361</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.102894300175496</v>
+        <v>0.1039916925830519</v>
       </c>
       <c r="T56">
-        <v>0.9888711300317439</v>
+        <v>1.007877925225176</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.2534417911673511</v>
       </c>
       <c r="W56">
-        <v>0.04785438118617279</v>
+        <v>0.05367753521506746</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.026478128268577</v>
+        <v>2.649096318924985</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07631890603066044</v>
+        <v>0.07632056496445627</v>
       </c>
       <c r="C57">
-        <v>128.4402616580324</v>
+        <v>125.2038865134817</v>
       </c>
       <c r="D57">
-        <v>277.6902616580325</v>
+        <v>277.6838865134818</v>
       </c>
       <c r="E57">
-        <v>-13.75</v>
+        <v>-10.51999999999998</v>
       </c>
       <c r="F57">
-        <v>177.65</v>
+        <v>180.88</v>
       </c>
       <c r="G57">
         <v>28.4</v>
@@ -5961,28 +5961,28 @@
         <v>33.837</v>
       </c>
       <c r="M57">
-        <v>12.773035</v>
+        <v>13.005272</v>
       </c>
       <c r="N57">
-        <v>21.063965</v>
+        <v>20.831728</v>
       </c>
       <c r="O57">
-        <v>5.338489018686394</v>
+        <v>5.27963045743106</v>
       </c>
       <c r="P57">
-        <v>15.72547598131361</v>
+        <v>15.55209754256894</v>
       </c>
       <c r="Q57">
-        <v>16.51347598131361</v>
+        <v>16.34009754256894</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1039916925830519</v>
+        <v>0.1051389664636784</v>
       </c>
       <c r="T57">
-        <v>1.007877925225176</v>
+        <v>1.027748665654674</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.649096318924985</v>
+        <v>2.60179102751561</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07632056496445627</v>
+        <v>0.07632222389825212</v>
       </c>
       <c r="C58">
-        <v>125.2038865134817</v>
+        <v>121.9675116616423</v>
       </c>
       <c r="D58">
-        <v>277.6838865134818</v>
+        <v>277.6775116616423</v>
       </c>
       <c r="E58">
-        <v>-10.51999999999998</v>
+        <v>-7.289999999999992</v>
       </c>
       <c r="F58">
-        <v>180.88</v>
+        <v>184.11</v>
       </c>
       <c r="G58">
         <v>28.4</v>
@@ -6043,28 +6043,28 @@
         <v>33.837</v>
       </c>
       <c r="M58">
-        <v>13.005272</v>
+        <v>13.237509</v>
       </c>
       <c r="N58">
-        <v>20.831728</v>
+        <v>20.599491</v>
       </c>
       <c r="O58">
-        <v>5.27963045743106</v>
+        <v>5.220771896175728</v>
       </c>
       <c r="P58">
-        <v>15.55209754256894</v>
+        <v>15.37871910382427</v>
       </c>
       <c r="Q58">
-        <v>16.34009754256894</v>
+        <v>16.16671910382427</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1051389664636784</v>
+        <v>0.1063396019201481</v>
       </c>
       <c r="T58">
-        <v>1.027748665654674</v>
+        <v>1.048543626569264</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.60179102751561</v>
+        <v>2.55614557089253</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07632222389825212</v>
+        <v>0.07632388283204797</v>
       </c>
       <c r="C59">
-        <v>121.9675116616423</v>
+        <v>118.7311371024939</v>
       </c>
       <c r="D59">
-        <v>277.6775116616423</v>
+        <v>277.671137102494</v>
       </c>
       <c r="E59">
-        <v>-7.289999999999992</v>
+        <v>-4.059999999999974</v>
       </c>
       <c r="F59">
-        <v>184.11</v>
+        <v>187.34</v>
       </c>
       <c r="G59">
         <v>28.4</v>
@@ -6125,28 +6125,28 @@
         <v>33.837</v>
       </c>
       <c r="M59">
-        <v>13.237509</v>
+        <v>13.469746</v>
       </c>
       <c r="N59">
-        <v>20.599491</v>
+        <v>20.367254</v>
       </c>
       <c r="O59">
-        <v>5.220771896175728</v>
+        <v>5.161913334920397</v>
       </c>
       <c r="P59">
-        <v>15.37871910382427</v>
+        <v>15.2053406650796</v>
       </c>
       <c r="Q59">
-        <v>16.16671910382427</v>
+        <v>15.9933406650796</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1063396019201481</v>
+        <v>0.1075974104935925</v>
       </c>
       <c r="T59">
-        <v>1.048543626569264</v>
+        <v>1.070328823717883</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.55614557089253</v>
+        <v>2.512074095532313</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07632388283204797</v>
+        <v>0.07804337220436773</v>
       </c>
       <c r="C60">
-        <v>118.731137102494</v>
+        <v>109.0476007994029</v>
       </c>
       <c r="D60">
-        <v>277.671137102494</v>
+        <v>271.2176007994029</v>
       </c>
       <c r="E60">
-        <v>-4.060000000000031</v>
+        <v>-0.8300000000000125</v>
       </c>
       <c r="F60">
-        <v>187.34</v>
+        <v>190.57</v>
       </c>
       <c r="G60">
         <v>28.4</v>
@@ -6207,45 +6207,45 @@
         <v>33.837</v>
       </c>
       <c r="M60">
-        <v>13.469746</v>
+        <v>14.445206</v>
       </c>
       <c r="N60">
-        <v>20.367254</v>
+        <v>19.391794</v>
       </c>
       <c r="O60">
-        <v>5.161913334920397</v>
+        <v>4.914691005308293</v>
       </c>
       <c r="P60">
-        <v>15.20534066507961</v>
+        <v>14.47710299469171</v>
       </c>
       <c r="Q60">
-        <v>15.99334066507961</v>
+        <v>15.26510299469171</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1075974104935925</v>
+        <v>0.1089165755828146</v>
       </c>
       <c r="T60">
-        <v>1.070328823717883</v>
+        <v>1.093176713410336</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.2534417911673511</v>
       </c>
       <c r="W60">
-        <v>0.05367753521506746</v>
+        <v>0.05658911222951479</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.512074095532314</v>
+        <v>2.342438037920678</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07804337220436773</v>
+        <v>0.07807414690830805</v>
       </c>
       <c r="C61">
-        <v>109.0476007994029</v>
+        <v>105.7048294802772</v>
       </c>
       <c r="D61">
-        <v>271.2176007994029</v>
+        <v>271.1048294802772</v>
       </c>
       <c r="E61">
-        <v>-0.8300000000000125</v>
+        <v>2.399999999999977</v>
       </c>
       <c r="F61">
-        <v>190.57</v>
+        <v>193.8</v>
       </c>
       <c r="G61">
         <v>28.4</v>
@@ -6289,28 +6289,28 @@
         <v>33.837</v>
       </c>
       <c r="M61">
-        <v>14.445206</v>
+        <v>14.69004</v>
       </c>
       <c r="N61">
-        <v>19.391794</v>
+        <v>19.14696</v>
       </c>
       <c r="O61">
-        <v>4.914691005308293</v>
+        <v>4.852639837809626</v>
       </c>
       <c r="P61">
-        <v>14.47710299469171</v>
+        <v>14.29432016219038</v>
       </c>
       <c r="Q61">
-        <v>15.26510299469171</v>
+        <v>15.08232016219038</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1089165755828146</v>
+        <v>0.1103016989264979</v>
       </c>
       <c r="T61">
-        <v>1.093176713410336</v>
+        <v>1.117166997587412</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.342438037920678</v>
+        <v>2.303397403955334</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07807414690830805</v>
+        <v>0.07810492161224836</v>
       </c>
       <c r="C62">
-        <v>105.7048294802772</v>
+        <v>102.3621519020057</v>
       </c>
       <c r="D62">
-        <v>271.1048294802772</v>
+        <v>270.9921519020057</v>
       </c>
       <c r="E62">
-        <v>2.399999999999977</v>
+        <v>5.629999999999995</v>
       </c>
       <c r="F62">
-        <v>193.8</v>
+        <v>197.03</v>
       </c>
       <c r="G62">
         <v>28.4</v>
@@ -6371,28 +6371,28 @@
         <v>33.837</v>
       </c>
       <c r="M62">
-        <v>14.69004</v>
+        <v>14.934874</v>
       </c>
       <c r="N62">
-        <v>19.14696</v>
+        <v>18.902126</v>
       </c>
       <c r="O62">
-        <v>4.852639837809626</v>
+        <v>4.790588670310958</v>
       </c>
       <c r="P62">
-        <v>14.29432016219038</v>
+        <v>14.11153732968904</v>
       </c>
       <c r="Q62">
-        <v>15.08232016219038</v>
+        <v>14.89953732968904</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1103016989264979</v>
+        <v>0.111757854236524</v>
       </c>
       <c r="T62">
-        <v>1.117166997587412</v>
+        <v>1.142387552747928</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.303397403955334</v>
+        <v>2.265636790775738</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07810492161224836</v>
+        <v>0.07813569631618869</v>
       </c>
       <c r="C63">
-        <v>102.3621519020057</v>
+        <v>99.01956794775401</v>
       </c>
       <c r="D63">
-        <v>270.9921519020057</v>
+        <v>270.879567947754</v>
       </c>
       <c r="E63">
-        <v>5.629999999999995</v>
+        <v>8.859999999999985</v>
       </c>
       <c r="F63">
-        <v>197.03</v>
+        <v>200.26</v>
       </c>
       <c r="G63">
         <v>28.4</v>
@@ -6453,28 +6453,28 @@
         <v>33.837</v>
       </c>
       <c r="M63">
-        <v>14.934874</v>
+        <v>15.179708</v>
       </c>
       <c r="N63">
-        <v>18.902126</v>
+        <v>18.65729200000001</v>
       </c>
       <c r="O63">
-        <v>4.790588670310958</v>
+        <v>4.728537502812292</v>
       </c>
       <c r="P63">
-        <v>14.11153732968904</v>
+        <v>13.92875449718771</v>
       </c>
       <c r="Q63">
-        <v>14.89953732968904</v>
+        <v>14.71675449718771</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.111757854236524</v>
+        <v>0.1132906492997093</v>
       </c>
       <c r="T63">
-        <v>1.142387552747928</v>
+        <v>1.168935505548472</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.265636790775738</v>
+        <v>2.229094261892258</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07813569631618869</v>
+        <v>0.078166471020129</v>
       </c>
       <c r="C64">
-        <v>99.01956794775401</v>
+        <v>95.67707750088226</v>
       </c>
       <c r="D64">
-        <v>270.879567947754</v>
+        <v>270.7670775008823</v>
       </c>
       <c r="E64">
-        <v>8.859999999999985</v>
+        <v>12.09</v>
       </c>
       <c r="F64">
-        <v>200.26</v>
+        <v>203.49</v>
       </c>
       <c r="G64">
         <v>28.4</v>
@@ -6535,28 +6535,28 @@
         <v>33.837</v>
       </c>
       <c r="M64">
-        <v>15.179708</v>
+        <v>15.424542</v>
       </c>
       <c r="N64">
-        <v>18.65729200000001</v>
+        <v>18.412458</v>
       </c>
       <c r="O64">
-        <v>4.728537502812292</v>
+        <v>4.666486335313623</v>
       </c>
       <c r="P64">
-        <v>13.92875449718771</v>
+        <v>13.74597166468638</v>
       </c>
       <c r="Q64">
-        <v>14.71675449718771</v>
+        <v>14.53397166468638</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1132906492997093</v>
+        <v>0.1149062981500937</v>
       </c>
       <c r="T64">
-        <v>1.168935505548472</v>
+        <v>1.19691848282472</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.229094261892258</v>
+        <v>2.193711813290793</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.078166471020129</v>
+        <v>0.07819724572406932</v>
       </c>
       <c r="C65">
-        <v>95.67707750088226</v>
+        <v>92.33468044494387</v>
       </c>
       <c r="D65">
-        <v>270.7670775008823</v>
+        <v>270.6546804449439</v>
       </c>
       <c r="E65">
-        <v>12.09</v>
+        <v>15.31999999999999</v>
       </c>
       <c r="F65">
-        <v>203.49</v>
+        <v>206.72</v>
       </c>
       <c r="G65">
         <v>28.4</v>
@@ -6617,28 +6617,28 @@
         <v>33.837</v>
       </c>
       <c r="M65">
-        <v>15.424542</v>
+        <v>15.669376</v>
       </c>
       <c r="N65">
-        <v>18.412458</v>
+        <v>18.167624</v>
       </c>
       <c r="O65">
-        <v>4.666486335313623</v>
+        <v>4.604435167814957</v>
       </c>
       <c r="P65">
-        <v>13.74597166468638</v>
+        <v>13.56318883218505</v>
       </c>
       <c r="Q65">
-        <v>14.53397166468638</v>
+        <v>14.35118883218505</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1149062981500937</v>
+        <v>0.116611705269944</v>
       </c>
       <c r="T65">
-        <v>1.19691848282472</v>
+        <v>1.226456069949648</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.193711813290793</v>
+        <v>2.159435066208125</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07819724572406932</v>
+        <v>0.07822802042800964</v>
       </c>
       <c r="C66">
-        <v>92.33468044494387</v>
+        <v>88.99237666368569</v>
       </c>
       <c r="D66">
-        <v>270.6546804449439</v>
+        <v>270.5423766636857</v>
       </c>
       <c r="E66">
-        <v>15.31999999999999</v>
+        <v>18.55000000000001</v>
       </c>
       <c r="F66">
-        <v>206.72</v>
+        <v>209.95</v>
       </c>
       <c r="G66">
         <v>28.4</v>
@@ -6699,28 +6699,28 @@
         <v>33.837</v>
       </c>
       <c r="M66">
-        <v>15.669376</v>
+        <v>15.91421</v>
       </c>
       <c r="N66">
-        <v>18.167624</v>
+        <v>17.92279</v>
       </c>
       <c r="O66">
-        <v>4.604435167814957</v>
+        <v>4.542384000316289</v>
       </c>
       <c r="P66">
-        <v>13.56318883218505</v>
+        <v>13.38040599968371</v>
       </c>
       <c r="Q66">
-        <v>14.35118883218505</v>
+        <v>14.16840599968371</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.116611705269944</v>
+        <v>0.1184145642252143</v>
       </c>
       <c r="T66">
-        <v>1.226456069949648</v>
+        <v>1.257681519196002</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.159435066208125</v>
+        <v>2.126212988266461</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07822802042800964</v>
+        <v>0.07825879513194994</v>
       </c>
       <c r="C67">
-        <v>88.99237666368569</v>
+        <v>85.6501660410475</v>
       </c>
       <c r="D67">
-        <v>270.5423766636857</v>
+        <v>270.4301660410475</v>
       </c>
       <c r="E67">
-        <v>18.55000000000001</v>
+        <v>21.78</v>
       </c>
       <c r="F67">
-        <v>209.95</v>
+        <v>213.18</v>
       </c>
       <c r="G67">
         <v>28.4</v>
@@ -6781,28 +6781,28 @@
         <v>33.837</v>
       </c>
       <c r="M67">
-        <v>15.91421</v>
+        <v>16.159044</v>
       </c>
       <c r="N67">
-        <v>17.92279</v>
+        <v>17.677956</v>
       </c>
       <c r="O67">
-        <v>4.542384000316289</v>
+        <v>4.480332832817622</v>
       </c>
       <c r="P67">
-        <v>13.38040599968371</v>
+        <v>13.19762316718238</v>
       </c>
       <c r="Q67">
-        <v>14.16840599968371</v>
+        <v>13.98562316718238</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1184145642252143</v>
+        <v>0.1203234737072653</v>
       </c>
       <c r="T67">
-        <v>1.257681519196002</v>
+        <v>1.290743759574493</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.126212988266461</v>
+        <v>2.093997639959394</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07825879513194994</v>
+        <v>0.07828956983589028</v>
       </c>
       <c r="C68">
-        <v>85.6501660410475</v>
+        <v>82.30804846116126</v>
       </c>
       <c r="D68">
-        <v>270.4301660410475</v>
+        <v>270.3180484611613</v>
       </c>
       <c r="E68">
-        <v>21.78</v>
+        <v>25.01000000000002</v>
       </c>
       <c r="F68">
-        <v>213.18</v>
+        <v>216.41</v>
       </c>
       <c r="G68">
         <v>28.4</v>
@@ -6863,28 +6863,28 @@
         <v>33.837</v>
       </c>
       <c r="M68">
-        <v>16.159044</v>
+        <v>16.403878</v>
       </c>
       <c r="N68">
-        <v>17.677956</v>
+        <v>17.433122</v>
       </c>
       <c r="O68">
-        <v>4.480332832817622</v>
+        <v>4.418281665318954</v>
       </c>
       <c r="P68">
-        <v>13.19762316718238</v>
+        <v>13.01484033468105</v>
       </c>
       <c r="Q68">
-        <v>13.98562316718238</v>
+        <v>13.80284033468105</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1203234737072653</v>
+        <v>0.1223480746730768</v>
       </c>
       <c r="T68">
-        <v>1.290743759574493</v>
+        <v>1.325809772097136</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.093997639959394</v>
+        <v>2.062743943840597</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07828956983589028</v>
+        <v>0.07832034453983058</v>
       </c>
       <c r="C69">
-        <v>82.30804846116126</v>
+        <v>78.96602380835142</v>
       </c>
       <c r="D69">
-        <v>270.3180484611613</v>
+        <v>270.2060238083515</v>
       </c>
       <c r="E69">
-        <v>25.01000000000002</v>
+        <v>28.24000000000001</v>
       </c>
       <c r="F69">
-        <v>216.41</v>
+        <v>219.64</v>
       </c>
       <c r="G69">
         <v>28.4</v>
@@ -6945,28 +6945,28 @@
         <v>33.837</v>
       </c>
       <c r="M69">
-        <v>16.403878</v>
+        <v>16.648712</v>
       </c>
       <c r="N69">
-        <v>17.433122</v>
+        <v>17.188288</v>
       </c>
       <c r="O69">
-        <v>4.418281665318954</v>
+        <v>4.356230497820287</v>
       </c>
       <c r="P69">
-        <v>13.01484033468105</v>
+        <v>12.83205750217971</v>
       </c>
       <c r="Q69">
-        <v>13.80284033468105</v>
+        <v>13.62005750217971</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1223480746730768</v>
+        <v>0.1244992131992517</v>
       </c>
       <c r="T69">
-        <v>1.325809772097136</v>
+        <v>1.363067410402444</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.062743943840597</v>
+        <v>2.032409474078235</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07832034453983058</v>
+        <v>0.0783511192437709</v>
       </c>
       <c r="C70">
-        <v>78.96602380835142</v>
+        <v>75.62409196713384</v>
       </c>
       <c r="D70">
-        <v>270.2060238083515</v>
+        <v>270.0940919671339</v>
       </c>
       <c r="E70">
-        <v>28.24000000000001</v>
+        <v>31.47</v>
       </c>
       <c r="F70">
-        <v>219.64</v>
+        <v>222.87</v>
       </c>
       <c r="G70">
         <v>28.4</v>
@@ -7027,28 +7027,28 @@
         <v>33.837</v>
       </c>
       <c r="M70">
-        <v>16.648712</v>
+        <v>16.893546</v>
       </c>
       <c r="N70">
-        <v>17.188288</v>
+        <v>16.943454</v>
       </c>
       <c r="O70">
-        <v>4.356230497820287</v>
+        <v>4.29417933032162</v>
       </c>
       <c r="P70">
-        <v>12.83205750217971</v>
+        <v>12.64927466967838</v>
       </c>
       <c r="Q70">
-        <v>13.62005750217971</v>
+        <v>13.43727466967838</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1244992131992517</v>
+        <v>0.1267891348561474</v>
       </c>
       <c r="T70">
-        <v>1.363067410402444</v>
+        <v>1.402728767308094</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.032409474078235</v>
+        <v>2.002954264308985</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0783511192437709</v>
+        <v>0.08580268254350774</v>
       </c>
       <c r="C71">
-        <v>75.62409196713384</v>
+        <v>47.77255934029705</v>
       </c>
       <c r="D71">
-        <v>270.0940919671339</v>
+        <v>245.4725593402971</v>
       </c>
       <c r="E71">
-        <v>31.47</v>
+        <v>34.70000000000002</v>
       </c>
       <c r="F71">
-        <v>222.87</v>
+        <v>226.1</v>
       </c>
       <c r="G71">
         <v>28.4</v>
@@ -7109,45 +7109,45 @@
         <v>33.837</v>
       </c>
       <c r="M71">
-        <v>16.893546</v>
+        <v>20.349</v>
       </c>
       <c r="N71">
-        <v>16.943454</v>
+        <v>13.488</v>
       </c>
       <c r="O71">
-        <v>4.29417933032162</v>
+        <v>3.418422879265233</v>
       </c>
       <c r="P71">
-        <v>12.64927466967838</v>
+        <v>10.06957712073477</v>
       </c>
       <c r="Q71">
-        <v>13.43727466967838</v>
+        <v>10.85757712073477</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1267891348561474</v>
+        <v>0.1292317179568362</v>
       </c>
       <c r="T71">
-        <v>1.402728767308094</v>
+        <v>1.445034214674121</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.2534417911673511</v>
       </c>
       <c r="W71">
-        <v>0.05658911222951479</v>
+        <v>0.06719023879493839</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.002954264308985</v>
+        <v>1.662833554474421</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08580268254350774</v>
+        <v>0.0859394685131023</v>
       </c>
       <c r="C72">
-        <v>47.77255934029705</v>
+        <v>44.13247708640651</v>
       </c>
       <c r="D72">
-        <v>245.4725593402971</v>
+        <v>245.0624770864065</v>
       </c>
       <c r="E72">
-        <v>34.70000000000002</v>
+        <v>37.93000000000001</v>
       </c>
       <c r="F72">
-        <v>226.1</v>
+        <v>229.33</v>
       </c>
       <c r="G72">
         <v>28.4</v>
@@ -7191,28 +7191,28 @@
         <v>33.837</v>
       </c>
       <c r="M72">
-        <v>20.349</v>
+        <v>20.6397</v>
       </c>
       <c r="N72">
-        <v>13.488</v>
+        <v>13.1973</v>
       </c>
       <c r="O72">
-        <v>3.418422879265233</v>
+        <v>3.344747350572883</v>
       </c>
       <c r="P72">
-        <v>10.06957712073477</v>
+        <v>9.852552649427119</v>
       </c>
       <c r="Q72">
-        <v>10.85757712073477</v>
+        <v>10.64055264942712</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1292317179568362</v>
+        <v>0.1318427550644691</v>
       </c>
       <c r="T72">
-        <v>1.445034214674121</v>
+        <v>1.490257279099874</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.662833554474421</v>
+        <v>1.639413363566331</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0859394685131023</v>
+        <v>0.08607625448269685</v>
       </c>
       <c r="C73">
-        <v>44.13247708640654</v>
+        <v>40.49376270016108</v>
       </c>
       <c r="D73">
-        <v>245.0624770864065</v>
+        <v>244.6537627001611</v>
       </c>
       <c r="E73">
-        <v>37.92999999999998</v>
+        <v>41.16</v>
       </c>
       <c r="F73">
-        <v>229.33</v>
+        <v>232.56</v>
       </c>
       <c r="G73">
         <v>28.4</v>
@@ -7273,28 +7273,28 @@
         <v>33.837</v>
       </c>
       <c r="M73">
-        <v>20.6397</v>
+        <v>20.9304</v>
       </c>
       <c r="N73">
-        <v>13.19730000000001</v>
+        <v>12.9066</v>
       </c>
       <c r="O73">
-        <v>3.344747350572884</v>
+        <v>3.271071821880535</v>
       </c>
       <c r="P73">
-        <v>9.852552649427121</v>
+        <v>9.63552817811947</v>
       </c>
       <c r="Q73">
-        <v>10.64055264942712</v>
+        <v>10.42352817811947</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1318427550644691</v>
+        <v>0.1346402948226472</v>
       </c>
       <c r="T73">
-        <v>1.490257279099873</v>
+        <v>1.53871056241318</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.639413363566331</v>
+        <v>1.616643733516799</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08607625448269685</v>
+        <v>0.0862130404522914</v>
       </c>
       <c r="C74">
-        <v>40.49376270016108</v>
+        <v>36.85640934898063</v>
       </c>
       <c r="D74">
-        <v>244.6537627001611</v>
+        <v>244.2464093489806</v>
       </c>
       <c r="E74">
-        <v>41.16</v>
+        <v>44.38999999999999</v>
       </c>
       <c r="F74">
-        <v>232.56</v>
+        <v>235.79</v>
       </c>
       <c r="G74">
         <v>28.4</v>
@@ -7355,28 +7355,28 @@
         <v>33.837</v>
       </c>
       <c r="M74">
-        <v>20.9304</v>
+        <v>21.2211</v>
       </c>
       <c r="N74">
-        <v>12.9066</v>
+        <v>12.6159</v>
       </c>
       <c r="O74">
-        <v>3.271071821880535</v>
+        <v>3.197396293188186</v>
       </c>
       <c r="P74">
-        <v>9.63552817811947</v>
+        <v>9.418503706811817</v>
       </c>
       <c r="Q74">
-        <v>10.42352817811947</v>
+        <v>10.20650370681182</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1346402948226472</v>
+        <v>0.1376450597480977</v>
       </c>
       <c r="T74">
-        <v>1.53871056241318</v>
+        <v>1.590752977823769</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.616643733516799</v>
+        <v>1.594497928948075</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0862130404522914</v>
+        <v>0.08634982642188596</v>
       </c>
       <c r="C75">
-        <v>36.85640934898063</v>
+        <v>33.2204102457151</v>
       </c>
       <c r="D75">
-        <v>244.2464093489806</v>
+        <v>243.8404102457151</v>
       </c>
       <c r="E75">
-        <v>44.38999999999999</v>
+        <v>47.62</v>
       </c>
       <c r="F75">
-        <v>235.79</v>
+        <v>239.02</v>
       </c>
       <c r="G75">
         <v>28.4</v>
@@ -7437,28 +7437,28 @@
         <v>33.837</v>
       </c>
       <c r="M75">
-        <v>21.2211</v>
+        <v>21.5118</v>
       </c>
       <c r="N75">
-        <v>12.6159</v>
+        <v>12.3252</v>
       </c>
       <c r="O75">
-        <v>3.197396293188186</v>
+        <v>3.123720764495836</v>
       </c>
       <c r="P75">
-        <v>9.418503706811817</v>
+        <v>9.201479235504166</v>
       </c>
       <c r="Q75">
-        <v>10.20650370681182</v>
+        <v>9.989479235504167</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1376450597480977</v>
+        <v>0.1408809604370444</v>
       </c>
       <c r="T75">
-        <v>1.590752977823769</v>
+        <v>1.646798655958249</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.594497928948075</v>
+        <v>1.572950659637966</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08634982642188596</v>
+        <v>0.08648661239148051</v>
       </c>
       <c r="C76">
-        <v>33.2204102457151</v>
+        <v>29.5857586482673</v>
       </c>
       <c r="D76">
-        <v>243.8404102457151</v>
+        <v>243.4357586482673</v>
       </c>
       <c r="E76">
-        <v>47.62</v>
+        <v>50.84999999999999</v>
       </c>
       <c r="F76">
-        <v>239.02</v>
+        <v>242.25</v>
       </c>
       <c r="G76">
         <v>28.4</v>
@@ -7519,28 +7519,28 @@
         <v>33.837</v>
       </c>
       <c r="M76">
-        <v>21.5118</v>
+        <v>21.8025</v>
       </c>
       <c r="N76">
-        <v>12.3252</v>
+        <v>12.0345</v>
       </c>
       <c r="O76">
-        <v>3.123720764495836</v>
+        <v>3.050045235803488</v>
       </c>
       <c r="P76">
-        <v>9.201479235504166</v>
+        <v>8.984454764196517</v>
       </c>
       <c r="Q76">
-        <v>9.989479235504167</v>
+        <v>9.772454764196517</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1408809604370444</v>
+        <v>0.1443757331811069</v>
       </c>
       <c r="T76">
-        <v>1.646798655958249</v>
+        <v>1.707327988343487</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.572950659637966</v>
+        <v>1.551977984176127</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08648661239148051</v>
+        <v>0.08662339836107506</v>
       </c>
       <c r="C77">
-        <v>29.5857586482673</v>
+        <v>25.95244785921969</v>
       </c>
       <c r="D77">
-        <v>243.4357586482673</v>
+        <v>243.0324478592197</v>
       </c>
       <c r="E77">
-        <v>50.84999999999999</v>
+        <v>54.07999999999998</v>
       </c>
       <c r="F77">
-        <v>242.25</v>
+        <v>245.48</v>
       </c>
       <c r="G77">
         <v>28.4</v>
@@ -7601,28 +7601,28 @@
         <v>33.837</v>
       </c>
       <c r="M77">
-        <v>21.8025</v>
+        <v>22.0932</v>
       </c>
       <c r="N77">
-        <v>12.0345</v>
+        <v>11.7438</v>
       </c>
       <c r="O77">
-        <v>3.050045235803488</v>
+        <v>2.976369707111139</v>
       </c>
       <c r="P77">
-        <v>8.984454764196517</v>
+        <v>8.767430292888864</v>
       </c>
       <c r="Q77">
-        <v>9.772454764196517</v>
+        <v>9.555430292888865</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1443757331811069</v>
+        <v>0.1481617369871745</v>
       </c>
       <c r="T77">
-        <v>1.707327988343487</v>
+        <v>1.772901431760829</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.551977984176127</v>
+        <v>1.531557221226441</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08662339836107506</v>
+        <v>0.08676018433066962</v>
       </c>
       <c r="C78">
-        <v>25.95244785921969</v>
+        <v>22.32047122546501</v>
       </c>
       <c r="D78">
-        <v>243.0324478592197</v>
+        <v>242.630471225465</v>
       </c>
       <c r="E78">
-        <v>54.07999999999998</v>
+        <v>57.31</v>
       </c>
       <c r="F78">
-        <v>245.48</v>
+        <v>248.71</v>
       </c>
       <c r="G78">
         <v>28.4</v>
@@ -7683,28 +7683,28 @@
         <v>33.837</v>
       </c>
       <c r="M78">
-        <v>22.0932</v>
+        <v>22.3839</v>
       </c>
       <c r="N78">
-        <v>11.7438</v>
+        <v>11.4531</v>
       </c>
       <c r="O78">
-        <v>2.976369707111139</v>
+        <v>2.90269417841879</v>
       </c>
       <c r="P78">
-        <v>8.767430292888864</v>
+        <v>8.550405821581213</v>
       </c>
       <c r="Q78">
-        <v>9.555430292888865</v>
+        <v>9.338405821581214</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1481617369871745</v>
+        <v>0.1522769585155089</v>
       </c>
       <c r="T78">
-        <v>1.772901431760829</v>
+        <v>1.8441769137362</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.531557221226441</v>
+        <v>1.511666867704019</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08676018433066962</v>
+        <v>0.1229543448014232</v>
       </c>
       <c r="C79">
-        <v>22.32047122546501</v>
+        <v>-54.7719730388857</v>
       </c>
       <c r="D79">
-        <v>242.630471225465</v>
+        <v>168.7680269611143</v>
       </c>
       <c r="E79">
-        <v>57.31</v>
+        <v>60.53999999999999</v>
       </c>
       <c r="F79">
-        <v>248.71</v>
+        <v>251.94</v>
       </c>
       <c r="G79">
         <v>28.4</v>
@@ -7765,45 +7765,45 @@
         <v>33.837</v>
       </c>
       <c r="M79">
-        <v>22.3839</v>
+        <v>36.98479200000001</v>
       </c>
       <c r="N79">
-        <v>11.4531</v>
+        <v>-3.147792000000003</v>
       </c>
       <c r="O79">
-        <v>2.90269417841879</v>
+        <v>-0.7977820427022592</v>
       </c>
       <c r="P79">
-        <v>8.550405821581213</v>
+        <v>-2.350009957297743</v>
       </c>
       <c r="Q79">
-        <v>9.338405821581214</v>
+        <v>-1.562009957297743</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1522769585155089</v>
+        <v>0.1590933191470498</v>
       </c>
       <c r="T79">
-        <v>1.8441769137362</v>
+        <v>1.962236023309254</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2534417911673511</v>
+        <v>0.2318712482614383</v>
       </c>
       <c r="W79">
-        <v>0.06719023879493839</v>
+        <v>0.1127613007552209</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.511666867704019</v>
+        <v>0.914889557848534</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1229543448014232</v>
+        <v>0.1239643448014232</v>
       </c>
       <c r="C80">
-        <v>-54.7719730388857</v>
+        <v>-59.42357378259203</v>
       </c>
       <c r="D80">
-        <v>168.7680269611143</v>
+        <v>167.346426217408</v>
       </c>
       <c r="E80">
-        <v>60.53999999999999</v>
+        <v>63.77000000000001</v>
       </c>
       <c r="F80">
-        <v>251.94</v>
+        <v>255.17</v>
       </c>
       <c r="G80">
         <v>28.4</v>
@@ -7847,37 +7847,37 @@
         <v>33.837</v>
       </c>
       <c r="M80">
-        <v>36.98479200000001</v>
+        <v>37.45895600000001</v>
       </c>
       <c r="N80">
-        <v>-3.147792000000003</v>
+        <v>-3.621956000000004</v>
       </c>
       <c r="O80">
-        <v>-0.7977820427022592</v>
+        <v>-0.9179550161693355</v>
       </c>
       <c r="P80">
-        <v>-2.350009957297743</v>
+        <v>-2.704000983830669</v>
       </c>
       <c r="Q80">
-        <v>-1.562009957297743</v>
+        <v>-1.916000983830669</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1590933191470498</v>
+        <v>0.1644882391064331</v>
       </c>
       <c r="T80">
-        <v>1.962236023309254</v>
+        <v>2.055675833943028</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2318712482614383</v>
+        <v>0.2289361691695214</v>
       </c>
       <c r="W80">
-        <v>0.1127613007552209</v>
+        <v>0.1131921703659143</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.914889557848534</v>
+        <v>0.9033086773694387</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1239643448014232</v>
+        <v>0.1249743448014232</v>
       </c>
       <c r="C81">
-        <v>-59.42357378259203</v>
+        <v>-64.05142515094849</v>
       </c>
       <c r="D81">
-        <v>167.346426217408</v>
+        <v>165.9485748490515</v>
       </c>
       <c r="E81">
-        <v>63.77000000000001</v>
+        <v>67.00000000000003</v>
       </c>
       <c r="F81">
-        <v>255.17</v>
+        <v>258.4</v>
       </c>
       <c r="G81">
         <v>28.4</v>
@@ -7929,37 +7929,37 @@
         <v>33.837</v>
       </c>
       <c r="M81">
-        <v>37.45895600000001</v>
+        <v>37.93312000000001</v>
       </c>
       <c r="N81">
-        <v>-3.621956000000004</v>
+        <v>-4.096120000000006</v>
       </c>
       <c r="O81">
-        <v>-0.9179550161693355</v>
+        <v>-1.038127989636412</v>
       </c>
       <c r="P81">
-        <v>-2.704000983830669</v>
+        <v>-3.057992010363594</v>
       </c>
       <c r="Q81">
-        <v>-1.916000983830669</v>
+        <v>-2.269992010363595</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1644882391064331</v>
+        <v>0.1704226510617548</v>
       </c>
       <c r="T81">
-        <v>2.055675833943028</v>
+        <v>2.15845962564018</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2289361691695214</v>
+        <v>0.2260744670549024</v>
       </c>
       <c r="W81">
-        <v>0.1131921703659143</v>
+        <v>0.1136122682363403</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9033086773694387</v>
+        <v>0.8920173189023206</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1249743448014232</v>
+        <v>0.1259843448014232</v>
       </c>
       <c r="C82">
-        <v>-64.05142515094849</v>
+        <v>-68.65611735235748</v>
       </c>
       <c r="D82">
-        <v>165.9485748490515</v>
+        <v>164.5738826476425</v>
       </c>
       <c r="E82">
-        <v>67.00000000000003</v>
+        <v>70.22999999999999</v>
       </c>
       <c r="F82">
-        <v>258.4</v>
+        <v>261.63</v>
       </c>
       <c r="G82">
         <v>28.4</v>
@@ -8011,37 +8011,37 @@
         <v>33.837</v>
       </c>
       <c r="M82">
-        <v>37.93312000000001</v>
+        <v>38.407284</v>
       </c>
       <c r="N82">
-        <v>-4.096120000000006</v>
+        <v>-4.570284000000001</v>
       </c>
       <c r="O82">
-        <v>-1.038127989636412</v>
+        <v>-1.158300963103486</v>
       </c>
       <c r="P82">
-        <v>-3.057992010363594</v>
+        <v>-3.411983036896514</v>
       </c>
       <c r="Q82">
-        <v>-2.269992010363595</v>
+        <v>-2.623983036896514</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1704226510617548</v>
+        <v>0.1769817379597419</v>
       </c>
       <c r="T82">
-        <v>2.15845962564018</v>
+        <v>2.272062763831769</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2260744670549024</v>
+        <v>0.2232834242517555</v>
       </c>
       <c r="W82">
-        <v>0.1136122682363403</v>
+        <v>0.1140219933198423</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8920173189023206</v>
+        <v>0.8810047594096995</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1259843448014232</v>
+        <v>0.1269943448014232</v>
       </c>
       <c r="C83">
-        <v>-68.65611735235748</v>
+        <v>-73.23822119911716</v>
       </c>
       <c r="D83">
-        <v>164.5738826476425</v>
+        <v>163.2217788008828</v>
       </c>
       <c r="E83">
-        <v>70.22999999999999</v>
+        <v>73.46000000000001</v>
       </c>
       <c r="F83">
-        <v>261.63</v>
+        <v>264.86</v>
       </c>
       <c r="G83">
         <v>28.4</v>
@@ -8093,37 +8093,37 @@
         <v>33.837</v>
       </c>
       <c r="M83">
-        <v>38.407284</v>
+        <v>38.88144800000001</v>
       </c>
       <c r="N83">
-        <v>-4.570284000000001</v>
+        <v>-5.044448000000003</v>
       </c>
       <c r="O83">
-        <v>-1.158300963103486</v>
+        <v>-1.278473936570563</v>
       </c>
       <c r="P83">
-        <v>-3.411983036896514</v>
+        <v>-3.76597406342944</v>
       </c>
       <c r="Q83">
-        <v>-2.623983036896514</v>
+        <v>-2.97797406342944</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1769817379597419</v>
+        <v>0.1842696122908387</v>
       </c>
       <c r="T83">
-        <v>2.272062763831769</v>
+        <v>2.398288472933533</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2232834242517555</v>
+        <v>0.2205604556633194</v>
       </c>
       <c r="W83">
-        <v>0.1140219933198423</v>
+        <v>0.1144217251086247</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8810047594096995</v>
+        <v>0.8702607989290934</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1269943448014232</v>
+        <v>0.1280043448014232</v>
       </c>
       <c r="C84">
-        <v>-73.23822119911716</v>
+        <v>-77.79828889769954</v>
       </c>
       <c r="D84">
-        <v>163.2217788008828</v>
+        <v>161.8917111023005</v>
       </c>
       <c r="E84">
-        <v>73.46000000000001</v>
+        <v>76.69000000000003</v>
       </c>
       <c r="F84">
-        <v>264.86</v>
+        <v>268.09</v>
       </c>
       <c r="G84">
         <v>28.4</v>
@@ -8175,37 +8175,37 @@
         <v>33.837</v>
       </c>
       <c r="M84">
-        <v>38.88144800000001</v>
+        <v>39.35561200000001</v>
       </c>
       <c r="N84">
-        <v>-5.044448000000003</v>
+        <v>-5.518612000000005</v>
       </c>
       <c r="O84">
-        <v>-1.278473936570563</v>
+        <v>-1.398646910037639</v>
       </c>
       <c r="P84">
-        <v>-3.76597406342944</v>
+        <v>-4.119965089962365</v>
       </c>
       <c r="Q84">
-        <v>-2.97797406342944</v>
+        <v>-3.331965089962365</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1842696122908387</v>
+        <v>0.1924148836020645</v>
       </c>
       <c r="T84">
-        <v>2.398288472933533</v>
+        <v>2.539364265459036</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2205604556633194</v>
+        <v>0.2179031007758095</v>
       </c>
       <c r="W84">
-        <v>0.1144217251086247</v>
+        <v>0.1148118248061112</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8702607989290934</v>
+        <v>0.8597757290624777</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1280043448014232</v>
+        <v>0.1290143448014232</v>
       </c>
       <c r="C85">
-        <v>-77.79828889769954</v>
+        <v>-82.33685480070267</v>
       </c>
       <c r="D85">
-        <v>161.8917111023005</v>
+        <v>160.5831451992974</v>
       </c>
       <c r="E85">
-        <v>76.69000000000003</v>
+        <v>79.92000000000004</v>
       </c>
       <c r="F85">
-        <v>268.09</v>
+        <v>271.3200000000001</v>
       </c>
       <c r="G85">
         <v>28.4</v>
@@ -8257,37 +8257,37 @@
         <v>33.837</v>
       </c>
       <c r="M85">
-        <v>39.35561200000001</v>
+        <v>39.82977600000001</v>
       </c>
       <c r="N85">
-        <v>-5.518612000000005</v>
+        <v>-5.992776000000006</v>
       </c>
       <c r="O85">
-        <v>-1.398646910037639</v>
+        <v>-1.518819883504715</v>
       </c>
       <c r="P85">
-        <v>-4.119965089962365</v>
+        <v>-4.473956116495291</v>
       </c>
       <c r="Q85">
-        <v>-3.331965089962365</v>
+        <v>-3.685956116495291</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1924148836020645</v>
+        <v>0.2015783138271935</v>
       </c>
       <c r="T85">
-        <v>2.539364265459036</v>
+        <v>2.698074532050226</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2179031007758095</v>
+        <v>0.2153090162427642</v>
       </c>
       <c r="W85">
-        <v>0.1148118248061112</v>
+        <v>0.1151926364155622</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8597757290624777</v>
+        <v>0.8495403037164958</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1290143448014232</v>
+        <v>0.1300243448014232</v>
       </c>
       <c r="C86">
-        <v>-82.33685480070261</v>
+        <v>-86.85443612262628</v>
       </c>
       <c r="D86">
-        <v>160.5831451992974</v>
+        <v>159.2955638773737</v>
       </c>
       <c r="E86">
-        <v>79.91999999999999</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="F86">
-        <v>271.32</v>
+        <v>274.55</v>
       </c>
       <c r="G86">
         <v>28.4</v>
@@ -8339,37 +8339,37 @@
         <v>33.837</v>
       </c>
       <c r="M86">
-        <v>39.829776</v>
+        <v>40.30394</v>
       </c>
       <c r="N86">
-        <v>-5.992775999999999</v>
+        <v>-6.466940000000001</v>
       </c>
       <c r="O86">
-        <v>-1.518819883504714</v>
+        <v>-1.63899285697179</v>
       </c>
       <c r="P86">
-        <v>-4.473956116495286</v>
+        <v>-4.827947143028211</v>
       </c>
       <c r="Q86">
-        <v>-3.685956116495285</v>
+        <v>-4.039947143028211</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2015783138271934</v>
+        <v>0.2119635347490063</v>
       </c>
       <c r="T86">
-        <v>2.698074532050224</v>
+        <v>2.877946167520239</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2153090162427642</v>
+        <v>0.2127759689928493</v>
       </c>
       <c r="W86">
-        <v>0.1151926364155622</v>
+        <v>0.1155644877518497</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8495403037164959</v>
+        <v>0.8395457119080665</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1300243448014232</v>
+        <v>0.1310343448014232</v>
       </c>
       <c r="C87">
-        <v>-86.85443612262628</v>
+        <v>-91.35153362148699</v>
       </c>
       <c r="D87">
-        <v>159.2955638773737</v>
+        <v>158.028466378513</v>
       </c>
       <c r="E87">
-        <v>83.15000000000001</v>
+        <v>86.37999999999997</v>
       </c>
       <c r="F87">
-        <v>274.55</v>
+        <v>277.78</v>
       </c>
       <c r="G87">
         <v>28.4</v>
@@ -8421,37 +8421,37 @@
         <v>33.837</v>
       </c>
       <c r="M87">
-        <v>40.30394</v>
+        <v>40.778104</v>
       </c>
       <c r="N87">
-        <v>-6.466940000000001</v>
+        <v>-6.941103999999996</v>
       </c>
       <c r="O87">
-        <v>-1.63899285697179</v>
+        <v>-1.759165830438864</v>
       </c>
       <c r="P87">
-        <v>-4.827947143028211</v>
+        <v>-5.181938169561131</v>
       </c>
       <c r="Q87">
-        <v>-4.039947143028211</v>
+        <v>-4.393938169561131</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2119635347490063</v>
+        <v>0.2238323586596497</v>
       </c>
       <c r="T87">
-        <v>2.877946167520239</v>
+        <v>3.083513750914542</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2127759689928493</v>
+        <v>0.2103018298185139</v>
       </c>
       <c r="W87">
-        <v>0.1155644877518497</v>
+        <v>0.1159276913826422</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8395457119080665</v>
+        <v>0.8297835524672752</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1310343448014232</v>
+        <v>0.1320443448014232</v>
       </c>
       <c r="C88">
-        <v>-91.35153362148699</v>
+        <v>-95.82863224815839</v>
       </c>
       <c r="D88">
-        <v>158.028466378513</v>
+        <v>156.7813677518416</v>
       </c>
       <c r="E88">
-        <v>86.37999999999997</v>
+        <v>89.60999999999999</v>
       </c>
       <c r="F88">
-        <v>277.78</v>
+        <v>281.01</v>
       </c>
       <c r="G88">
         <v>28.4</v>
@@ -8503,37 +8503,37 @@
         <v>33.837</v>
       </c>
       <c r="M88">
-        <v>40.778104</v>
+        <v>41.252268</v>
       </c>
       <c r="N88">
-        <v>-6.941103999999996</v>
+        <v>-7.415267999999998</v>
       </c>
       <c r="O88">
-        <v>-1.759165830438864</v>
+        <v>-1.879338803905941</v>
       </c>
       <c r="P88">
-        <v>-5.181938169561131</v>
+        <v>-5.535929196094057</v>
       </c>
       <c r="Q88">
-        <v>-4.393938169561131</v>
+        <v>-4.747929196094057</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2238323586596497</v>
+        <v>0.2375271554796227</v>
       </c>
       <c r="T88">
-        <v>3.083513750914542</v>
+        <v>3.320707116369507</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2103018298185139</v>
+        <v>0.2078845674068068</v>
       </c>
       <c r="W88">
-        <v>0.1159276913826422</v>
+        <v>0.1162825455046808</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8297835524672752</v>
+        <v>0.8202458104848926</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1320443448014232</v>
+        <v>0.1330543448014232</v>
       </c>
       <c r="C89">
-        <v>-95.82863224815839</v>
+        <v>-100.2862017652066</v>
       </c>
       <c r="D89">
-        <v>156.7813677518416</v>
+        <v>155.5537982347934</v>
       </c>
       <c r="E89">
-        <v>89.60999999999999</v>
+        <v>92.84</v>
       </c>
       <c r="F89">
-        <v>281.01</v>
+        <v>284.24</v>
       </c>
       <c r="G89">
         <v>28.4</v>
@@ -8585,37 +8585,37 @@
         <v>33.837</v>
       </c>
       <c r="M89">
-        <v>41.252268</v>
+        <v>41.726432</v>
       </c>
       <c r="N89">
-        <v>-7.415267999999998</v>
+        <v>-7.889431999999999</v>
       </c>
       <c r="O89">
-        <v>-1.879338803905941</v>
+        <v>-1.999511777373017</v>
       </c>
       <c r="P89">
-        <v>-5.535929196094057</v>
+        <v>-5.889920222626983</v>
       </c>
       <c r="Q89">
-        <v>-4.747929196094057</v>
+        <v>-5.101920222626982</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2375271554796227</v>
+        <v>0.2535044184362579</v>
       </c>
       <c r="T89">
-        <v>3.320707116369507</v>
+        <v>3.597432709400299</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2078845674068068</v>
+        <v>0.205522242777184</v>
       </c>
       <c r="W89">
-        <v>0.1162825455046808</v>
+        <v>0.1166293347603094</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8202458104848926</v>
+        <v>0.8109248353657461</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1330543448014232</v>
+        <v>0.1340643448014232</v>
       </c>
       <c r="C90">
-        <v>-100.2862017652066</v>
+        <v>-104.7246973368789</v>
       </c>
       <c r="D90">
-        <v>155.5537982347934</v>
+        <v>154.3453026631211</v>
       </c>
       <c r="E90">
-        <v>92.84</v>
+        <v>96.07000000000002</v>
       </c>
       <c r="F90">
-        <v>284.24</v>
+        <v>287.47</v>
       </c>
       <c r="G90">
         <v>28.4</v>
@@ -8667,37 +8667,37 @@
         <v>33.837</v>
       </c>
       <c r="M90">
-        <v>41.726432</v>
+        <v>42.200596</v>
       </c>
       <c r="N90">
-        <v>-7.889431999999999</v>
+        <v>-8.363596000000001</v>
       </c>
       <c r="O90">
-        <v>-1.999511777373017</v>
+        <v>-2.119684750840093</v>
       </c>
       <c r="P90">
-        <v>-5.889920222626983</v>
+        <v>-6.243911249159908</v>
       </c>
       <c r="Q90">
-        <v>-5.101920222626982</v>
+        <v>-5.455911249159907</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2535044184362579</v>
+        <v>0.2723866382940996</v>
       </c>
       <c r="T90">
-        <v>3.597432709400299</v>
+        <v>3.924472046618508</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.205522242777184</v>
+        <v>0.2032130040942943</v>
       </c>
       <c r="W90">
-        <v>0.1166293347603094</v>
+        <v>0.1169683309989576</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8109248353657461</v>
+        <v>0.8018133203616367</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1340643448014232</v>
+        <v>0.1851542713991078</v>
       </c>
       <c r="C91">
-        <v>-104.7246973368789</v>
+        <v>-151.498329773594</v>
       </c>
       <c r="D91">
-        <v>154.3453026631211</v>
+        <v>110.801670226406</v>
       </c>
       <c r="E91">
-        <v>96.07000000000002</v>
+        <v>99.29999999999998</v>
       </c>
       <c r="F91">
-        <v>287.47</v>
+        <v>290.7</v>
       </c>
       <c r="G91">
         <v>28.4</v>
@@ -8749,45 +8749,45 @@
         <v>33.837</v>
       </c>
       <c r="M91">
-        <v>42.200596</v>
+        <v>58.37256</v>
       </c>
       <c r="N91">
-        <v>-8.363596000000001</v>
+        <v>-24.53556</v>
       </c>
       <c r="O91">
-        <v>-2.119684750840093</v>
+        <v>-6.218336273694012</v>
       </c>
       <c r="P91">
-        <v>-6.243911249159908</v>
+        <v>-18.31722372630598</v>
       </c>
       <c r="Q91">
-        <v>-5.455911249159907</v>
+        <v>-17.52922372630598</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2723866382940996</v>
+        <v>0.309844568100355</v>
       </c>
       <c r="T91">
-        <v>3.924472046618508</v>
+        <v>4.573241980960553</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.2032130040942943</v>
+        <v>0.1469133765544917</v>
       </c>
       <c r="W91">
-        <v>0.1169683309989576</v>
+        <v>0.1712997939878581</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8018133203616367</v>
+        <v>0.5796730518586131</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1851542713991078</v>
+        <v>0.1867042713991078</v>
       </c>
       <c r="C92">
-        <v>-151.498329773594</v>
+        <v>-155.6686431550662</v>
       </c>
       <c r="D92">
-        <v>110.801670226406</v>
+        <v>109.8613568449338</v>
       </c>
       <c r="E92">
-        <v>99.29999999999998</v>
+        <v>102.53</v>
       </c>
       <c r="F92">
-        <v>290.7</v>
+        <v>293.93</v>
       </c>
       <c r="G92">
         <v>28.4</v>
@@ -8831,37 +8831,37 @@
         <v>33.837</v>
       </c>
       <c r="M92">
-        <v>58.37256</v>
+        <v>59.02114400000001</v>
       </c>
       <c r="N92">
-        <v>-24.53556</v>
+        <v>-25.184144</v>
       </c>
       <c r="O92">
-        <v>-6.218336273694012</v>
+        <v>-6.382714564376499</v>
       </c>
       <c r="P92">
-        <v>-18.31722372630598</v>
+        <v>-18.8014294356235</v>
       </c>
       <c r="Q92">
-        <v>-17.52922372630598</v>
+        <v>-18.0134294356235</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.309844568100355</v>
+        <v>0.3391828534448389</v>
       </c>
       <c r="T92">
-        <v>4.573241980960553</v>
+        <v>5.081379978845059</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1469133765544917</v>
+        <v>0.1452989438451017</v>
       </c>
       <c r="W92">
-        <v>0.1712997939878581</v>
+        <v>0.1716239720759036</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5796730518586131</v>
+        <v>0.5733030183217052</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1867042713991078</v>
+        <v>0.1882542713991078</v>
       </c>
       <c r="C93">
-        <v>-155.6686431550662</v>
+        <v>-159.8231309850882</v>
       </c>
       <c r="D93">
-        <v>109.8613568449338</v>
+        <v>108.9368690149118</v>
       </c>
       <c r="E93">
-        <v>102.53</v>
+        <v>105.76</v>
       </c>
       <c r="F93">
-        <v>293.93</v>
+        <v>297.16</v>
       </c>
       <c r="G93">
         <v>28.4</v>
@@ -8913,37 +8913,37 @@
         <v>33.837</v>
       </c>
       <c r="M93">
-        <v>59.02114400000001</v>
+        <v>59.66972800000001</v>
       </c>
       <c r="N93">
-        <v>-25.184144</v>
+        <v>-25.832728</v>
       </c>
       <c r="O93">
-        <v>-6.382714564376499</v>
+        <v>-6.547092855058985</v>
       </c>
       <c r="P93">
-        <v>-18.8014294356235</v>
+        <v>-19.28563514494102</v>
       </c>
       <c r="Q93">
-        <v>-18.0134294356235</v>
+        <v>-18.49763514494102</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3391828534448389</v>
+        <v>0.3758557101254439</v>
       </c>
       <c r="T93">
-        <v>5.081379978845059</v>
+        <v>5.716552476200693</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1452989438451017</v>
+        <v>0.1437196074989593</v>
       </c>
       <c r="W93">
-        <v>0.1716239720759036</v>
+        <v>0.171941102814209</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5733030183217052</v>
+        <v>0.5670714637747301</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1882542713991078</v>
+        <v>0.1898042713991078</v>
       </c>
       <c r="C94">
-        <v>-159.8231309850882</v>
+        <v>-163.9621894477507</v>
       </c>
       <c r="D94">
-        <v>108.9368690149118</v>
+        <v>108.0278105522493</v>
       </c>
       <c r="E94">
-        <v>105.76</v>
+        <v>108.99</v>
       </c>
       <c r="F94">
-        <v>297.16</v>
+        <v>300.39</v>
       </c>
       <c r="G94">
         <v>28.4</v>
@@ -8995,37 +8995,37 @@
         <v>33.837</v>
       </c>
       <c r="M94">
-        <v>59.66972800000001</v>
+        <v>60.31831200000001</v>
       </c>
       <c r="N94">
-        <v>-25.832728</v>
+        <v>-26.48131200000001</v>
       </c>
       <c r="O94">
-        <v>-6.547092855058985</v>
+        <v>-6.711471145741471</v>
       </c>
       <c r="P94">
-        <v>-19.28563514494102</v>
+        <v>-19.76984085425854</v>
       </c>
       <c r="Q94">
-        <v>-18.49763514494102</v>
+        <v>-18.98184085425854</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3758557101254439</v>
+        <v>0.4230065258576502</v>
       </c>
       <c r="T94">
-        <v>5.716552476200693</v>
+        <v>6.533202829943651</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1437196074989593</v>
+        <v>0.1421742353753145</v>
       </c>
       <c r="W94">
-        <v>0.171941102814209</v>
+        <v>0.1722514135366369</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5670714637747301</v>
+        <v>0.5609739211534964</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1898042713991078</v>
+        <v>0.1913542713991078</v>
       </c>
       <c r="C95">
-        <v>-163.9621894477507</v>
+        <v>-168.0862016122479</v>
       </c>
       <c r="D95">
-        <v>108.0278105522493</v>
+        <v>107.1337983877522</v>
       </c>
       <c r="E95">
-        <v>108.99</v>
+        <v>112.22</v>
       </c>
       <c r="F95">
-        <v>300.39</v>
+        <v>303.62</v>
       </c>
       <c r="G95">
         <v>28.4</v>
@@ -9077,37 +9077,37 @@
         <v>33.837</v>
       </c>
       <c r="M95">
-        <v>60.31831200000001</v>
+        <v>60.96689600000001</v>
       </c>
       <c r="N95">
-        <v>-26.48131200000001</v>
+        <v>-27.129896</v>
       </c>
       <c r="O95">
-        <v>-6.711471145741471</v>
+        <v>-6.875849436423954</v>
       </c>
       <c r="P95">
-        <v>-19.76984085425854</v>
+        <v>-20.25404656357605</v>
       </c>
       <c r="Q95">
-        <v>-18.98184085425854</v>
+        <v>-19.46604656357605</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4230065258576502</v>
+        <v>0.4858742801672586</v>
       </c>
       <c r="T95">
-        <v>6.533202829943651</v>
+        <v>7.622069968267594</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1421742353753145</v>
+        <v>0.1406617435096197</v>
       </c>
       <c r="W95">
-        <v>0.1722514135366369</v>
+        <v>0.1725551219032684</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5609739211534964</v>
+        <v>0.5550061134816507</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1913542713991078</v>
+        <v>0.1929042713991078</v>
       </c>
       <c r="C96">
-        <v>-168.0862016122479</v>
+        <v>-172.1955379711014</v>
       </c>
       <c r="D96">
-        <v>107.1337983877522</v>
+        <v>106.2544620288986</v>
       </c>
       <c r="E96">
-        <v>112.22</v>
+        <v>115.45</v>
       </c>
       <c r="F96">
-        <v>303.62</v>
+        <v>306.85</v>
       </c>
       <c r="G96">
         <v>28.4</v>
@@ -9159,37 +9159,37 @@
         <v>33.837</v>
       </c>
       <c r="M96">
-        <v>60.96689600000001</v>
+        <v>61.61548000000001</v>
       </c>
       <c r="N96">
-        <v>-27.129896</v>
+        <v>-27.77848</v>
       </c>
       <c r="O96">
-        <v>-6.875849436423954</v>
+        <v>-7.04022772710644</v>
       </c>
       <c r="P96">
-        <v>-20.25404656357605</v>
+        <v>-20.73825227289356</v>
       </c>
       <c r="Q96">
-        <v>-19.46604656357605</v>
+        <v>-19.95025227289356</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4858742801672586</v>
+        <v>0.5738891362007106</v>
       </c>
       <c r="T96">
-        <v>7.622069968267594</v>
+        <v>9.146483961921117</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1406617435096197</v>
+        <v>0.1391810935779395</v>
       </c>
       <c r="W96">
-        <v>0.1725551219032684</v>
+        <v>0.1728524364095498</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5550061134816507</v>
+        <v>0.5491639438660545</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1929042713991078</v>
+        <v>0.1944542713991078</v>
       </c>
       <c r="C97">
-        <v>-172.1955379711014</v>
+        <v>-176.2905569520951</v>
       </c>
       <c r="D97">
-        <v>106.2544620288986</v>
+        <v>105.389443047905</v>
       </c>
       <c r="E97">
-        <v>115.45</v>
+        <v>118.68</v>
       </c>
       <c r="F97">
-        <v>306.85</v>
+        <v>310.08</v>
       </c>
       <c r="G97">
         <v>28.4</v>
@@ -9241,37 +9241,37 @@
         <v>33.837</v>
       </c>
       <c r="M97">
-        <v>61.61548000000001</v>
+        <v>62.26406400000001</v>
       </c>
       <c r="N97">
-        <v>-27.77848</v>
+        <v>-28.42706400000001</v>
       </c>
       <c r="O97">
-        <v>-7.04022772710644</v>
+        <v>-7.204606017788927</v>
       </c>
       <c r="P97">
-        <v>-20.73825227289356</v>
+        <v>-21.22245798221108</v>
       </c>
       <c r="Q97">
-        <v>-19.95025227289356</v>
+        <v>-20.43445798221108</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5738891362007106</v>
+        <v>0.7059114202508885</v>
       </c>
       <c r="T97">
-        <v>9.146483961921117</v>
+        <v>11.4331049524014</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1391810935779395</v>
+        <v>0.1377312905198359</v>
       </c>
       <c r="W97">
-        <v>0.1728524364095498</v>
+        <v>0.173143556863617</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5491639438660545</v>
+        <v>0.5434434861174496</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1944542713991078</v>
+        <v>0.1960042713991078</v>
       </c>
       <c r="C98">
-        <v>-176.290556952095</v>
+        <v>-180.3716054054045</v>
       </c>
       <c r="D98">
-        <v>105.389443047905</v>
+        <v>104.5383945945955</v>
       </c>
       <c r="E98">
-        <v>118.68</v>
+        <v>121.91</v>
       </c>
       <c r="F98">
-        <v>310.08</v>
+        <v>313.31</v>
       </c>
       <c r="G98">
         <v>28.4</v>
@@ -9323,37 +9323,37 @@
         <v>33.837</v>
       </c>
       <c r="M98">
-        <v>62.264064</v>
+        <v>62.912648</v>
       </c>
       <c r="N98">
-        <v>-28.42706399999999</v>
+        <v>-29.075648</v>
       </c>
       <c r="O98">
-        <v>-7.204606017788923</v>
+        <v>-7.36898430847141</v>
       </c>
       <c r="P98">
-        <v>-21.22245798221107</v>
+        <v>-21.70666369152859</v>
       </c>
       <c r="Q98">
-        <v>-20.43445798221107</v>
+        <v>-20.91866369152859</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7059114202508866</v>
+        <v>0.9259485603345157</v>
       </c>
       <c r="T98">
-        <v>11.43310495240137</v>
+        <v>15.24413993653516</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.137731290519836</v>
+        <v>0.1363113803082913</v>
       </c>
       <c r="W98">
-        <v>0.1731435568636169</v>
+        <v>0.1734286748340951</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5434434861174497</v>
+        <v>0.5378409759512904</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1960042713991078</v>
+        <v>0.1975542713991078</v>
       </c>
       <c r="C99">
-        <v>-180.3716054054045</v>
+        <v>-184.4390190673149</v>
       </c>
       <c r="D99">
-        <v>104.5383945945955</v>
+        <v>103.7009809326852</v>
       </c>
       <c r="E99">
-        <v>121.91</v>
+        <v>125.14</v>
       </c>
       <c r="F99">
-        <v>313.31</v>
+        <v>316.54</v>
       </c>
       <c r="G99">
         <v>28.4</v>
@@ -9405,37 +9405,37 @@
         <v>33.837</v>
       </c>
       <c r="M99">
-        <v>62.912648</v>
+        <v>63.561232</v>
       </c>
       <c r="N99">
-        <v>-29.075648</v>
+        <v>-29.724232</v>
       </c>
       <c r="O99">
-        <v>-7.36898430847141</v>
+        <v>-7.533362599153895</v>
       </c>
       <c r="P99">
-        <v>-21.70666369152859</v>
+        <v>-22.1908694008461</v>
       </c>
       <c r="Q99">
-        <v>-20.91866369152859</v>
+        <v>-21.4028694008461</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9259485603345157</v>
+        <v>1.366022840501774</v>
       </c>
       <c r="T99">
-        <v>15.24413993653516</v>
+        <v>22.86620990480274</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1363113803082913</v>
+        <v>0.1349204478561658</v>
       </c>
       <c r="W99">
-        <v>0.1734286748340951</v>
+        <v>0.1737079740704819</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5378409759512904</v>
+        <v>0.5323528027272977</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1975542713991078</v>
+        <v>0.1991042713991077</v>
       </c>
       <c r="C100">
-        <v>-184.4390190673149</v>
+        <v>-188.4931230018265</v>
       </c>
       <c r="D100">
-        <v>103.7009809326852</v>
+        <v>102.8768769981735</v>
       </c>
       <c r="E100">
-        <v>125.14</v>
+        <v>128.37</v>
       </c>
       <c r="F100">
-        <v>316.54</v>
+        <v>319.77</v>
       </c>
       <c r="G100">
         <v>28.4</v>
@@ -9487,37 +9487,37 @@
         <v>33.837</v>
       </c>
       <c r="M100">
-        <v>63.561232</v>
+        <v>64.209816</v>
       </c>
       <c r="N100">
-        <v>-29.724232</v>
+        <v>-30.372816</v>
       </c>
       <c r="O100">
-        <v>-7.533362599153895</v>
+        <v>-7.69774088983638</v>
       </c>
       <c r="P100">
-        <v>-22.1908694008461</v>
+        <v>-22.67507511016362</v>
       </c>
       <c r="Q100">
-        <v>-21.4028694008461</v>
+        <v>-21.88707511016362</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.366022840501774</v>
+        <v>2.686245681003547</v>
       </c>
       <c r="T100">
-        <v>22.86620990480274</v>
+        <v>45.73241980960548</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1349204478561658</v>
+        <v>0.1335576150495379</v>
       </c>
       <c r="W100">
-        <v>0.1737079740704819</v>
+        <v>0.1739816308980528</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5323528027272977</v>
+        <v>0.5269755016896482</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1991042713991077</v>
-      </c>
-      <c r="C101">
-        <v>-188.4931230018265</v>
-      </c>
-      <c r="D101">
-        <v>102.8768769981735</v>
-      </c>
-      <c r="E101">
-        <v>128.37</v>
-      </c>
-      <c r="F101">
-        <v>319.77</v>
-      </c>
-      <c r="G101">
-        <v>28.4</v>
-      </c>
-      <c r="H101">
-        <v>131.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34.625</v>
-      </c>
-      <c r="K101">
-        <v>0.788</v>
-      </c>
-      <c r="L101">
-        <v>33.837</v>
-      </c>
-      <c r="M101">
-        <v>64.209816</v>
-      </c>
-      <c r="N101">
-        <v>-30.372816</v>
-      </c>
-      <c r="O101">
-        <v>-7.69774088983638</v>
-      </c>
-      <c r="P101">
-        <v>-22.67507511016362</v>
-      </c>
-      <c r="Q101">
-        <v>-21.88707511016362</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.686245681003547</v>
-      </c>
-      <c r="T101">
-        <v>45.73241980960548</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1335576150495379</v>
-      </c>
-      <c r="W101">
-        <v>0.1739816308980528</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5269755016896482</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
